--- a/base_datas/mediana_uf_detalhamento.xlsx
+++ b/base_datas/mediana_uf_detalhamento.xlsx
@@ -603,22 +603,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>283.9583954907779</v>
+        <v>285.5637434237151</v>
       </c>
       <c r="C2">
-        <v>39.80510115453872</v>
+        <v>39.35472068928102</v>
       </c>
       <c r="D2">
-        <v>4759.685129558606</v>
+        <v>4739.746970517682</v>
       </c>
       <c r="E2">
-        <v>145.0513119290826</v>
+        <v>147.8351081595781</v>
       </c>
       <c r="F2">
-        <v>279.239839568117</v>
+        <v>285.5560643464185</v>
       </c>
       <c r="G2">
-        <v>11.10129639374646</v>
+        <v>10.94486028033211</v>
       </c>
       <c r="H2">
         <v>34.49796639466256</v>
@@ -627,49 +627,49 @@
         <v>146.1711518736456</v>
       </c>
       <c r="J2">
-        <v>39.80510115453872</v>
+        <v>39.35472068928102</v>
       </c>
       <c r="K2">
         <v>-9.57655712571925E-15</v>
       </c>
       <c r="L2">
-        <v>2739.744731038375</v>
+        <v>2573.469552814637</v>
       </c>
       <c r="M2">
-        <v>770.5855750411912</v>
+        <v>770.8154368180764</v>
       </c>
       <c r="N2">
-        <v>1313.985043231271</v>
+        <v>1368.07551264525</v>
       </c>
       <c r="O2">
-        <v>121.9991253113552</v>
+        <v>124.4543191006258</v>
       </c>
       <c r="P2">
         <v>5.567369628518485</v>
       </c>
       <c r="S2">
-        <v>0.3205017313855276</v>
+        <v>0.3016065529856479</v>
       </c>
       <c r="T2">
-        <v>8.254262402294792</v>
+        <v>9.335962311209643</v>
       </c>
       <c r="U2">
-        <v>20.20036474962382</v>
+        <v>15.10645675752819</v>
       </c>
       <c r="V2">
-        <v>90.02096352252764</v>
+        <v>90.21163015555872</v>
       </c>
       <c r="W2">
-        <v>130.1075390437837</v>
+        <v>136.0283599374022</v>
       </c>
       <c r="Z2">
-        <v>2.941785340737871E-14</v>
+        <v>3.226141660715943E-14</v>
       </c>
       <c r="AA2">
-        <v>4.732662670168948</v>
+        <v>4.553415579119087</v>
       </c>
       <c r="AB2">
-        <v>8.802885619871919</v>
+        <v>8.201769280205655</v>
       </c>
       <c r="AC2">
         <v>-1.408619160560911E-16</v>
@@ -678,43 +678,43 @@
         <v>34.49796639466256</v>
       </c>
       <c r="AH2">
-        <v>1420.316144546597</v>
+        <v>1404.303908179653</v>
       </c>
       <c r="AJ2">
-        <v>24.43361282342864</v>
+        <v>24.12032175887468</v>
       </c>
       <c r="AK2">
-        <v>697.5568566191579</v>
+        <v>686.7130289203085</v>
       </c>
       <c r="AL2">
-        <v>138.6253725730148</v>
+        <v>141.2635355567593</v>
       </c>
       <c r="AM2">
-        <v>210.4724438042965</v>
+        <v>219.4668180762981</v>
       </c>
       <c r="AN2">
-        <v>32.21932287438311</v>
+        <v>31.03121001611841</v>
       </c>
       <c r="AO2">
-        <v>207.7041951684839</v>
+        <v>200.9404325653403</v>
       </c>
       <c r="AP2">
-        <v>647.8717564960864</v>
+        <v>656.8697915402968</v>
       </c>
       <c r="AQ2">
-        <v>43.65787379404382</v>
+        <v>42.66190784081595</v>
       </c>
       <c r="AR2">
-        <v>2.489077104813607</v>
+        <v>2.476773082942097</v>
       </c>
       <c r="AS2">
-        <v>6.021043940264216</v>
+        <v>6.033916857977701</v>
       </c>
       <c r="AT2">
         <v>0.04486931973408614</v>
       </c>
       <c r="AU2">
-        <v>40.44255735079063</v>
+        <v>46.12002249357328</v>
       </c>
       <c r="AV2">
         <v>1</v>
@@ -730,10 +730,10 @@
         <v>341.2111347016007</v>
       </c>
       <c r="C3">
-        <v>259.3472432054568</v>
+        <v>261.40361102601</v>
       </c>
       <c r="D3">
-        <v>8018.469716132185</v>
+        <v>7982.322781391018</v>
       </c>
       <c r="E3">
         <v>231.9742618959338</v>
@@ -742,16 +742,16 @@
         <v>327.6135269189371</v>
       </c>
       <c r="G3">
-        <v>9.009045629556811</v>
+        <v>8.935345509813867</v>
       </c>
       <c r="H3">
-        <v>82.99977930805608</v>
+        <v>85.54520903574972</v>
       </c>
       <c r="I3">
-        <v>198.5066795515491</v>
+        <v>199.3934640795206</v>
       </c>
       <c r="J3">
-        <v>102.6400065879698</v>
+        <v>102.5030161090458</v>
       </c>
       <c r="K3">
         <v>1.159420708809301E-14</v>
@@ -760,37 +760,37 @@
         <v>5257.196750971281</v>
       </c>
       <c r="M3">
-        <v>1041.368728120803</v>
+        <v>1032.827548729685</v>
       </c>
       <c r="N3">
         <v>1566.593200656242</v>
       </c>
       <c r="O3">
-        <v>180.8912265697908</v>
+        <v>177.721577095833</v>
       </c>
       <c r="P3">
-        <v>40.19938480128923</v>
+        <v>41.60439422008151</v>
       </c>
       <c r="S3">
-        <v>11.13753632755408</v>
+        <v>11.29426860223071</v>
       </c>
       <c r="T3">
-        <v>6.021365230217262</v>
+        <v>6.739001045162713</v>
       </c>
       <c r="U3">
         <v>5.831349378575656</v>
       </c>
       <c r="V3">
-        <v>100.8135594191041</v>
+        <v>100.706403956017</v>
       </c>
       <c r="W3">
         <v>160.0005603313581</v>
       </c>
       <c r="Z3">
-        <v>2.385078362492537E-14</v>
+        <v>2.424441846872607E-14</v>
       </c>
       <c r="AA3">
-        <v>7.025822281167109</v>
+        <v>7.036268611015609</v>
       </c>
       <c r="AB3">
         <v>3.020586624262398</v>
@@ -802,13 +802,13 @@
         <v>69.36389114743217</v>
       </c>
       <c r="AF3">
-        <v>108.3593809423199</v>
+        <v>105.2351290063619</v>
       </c>
       <c r="AG3">
         <v>0.1124137542488116</v>
       </c>
       <c r="AH3">
-        <v>2588.354052280334</v>
+        <v>2564.900011632566</v>
       </c>
       <c r="AJ3">
         <v>50.31833502661729</v>
@@ -826,22 +826,22 @@
         <v>35.00160496444995</v>
       </c>
       <c r="AO3">
-        <v>18.87146364271179</v>
+        <v>19.46276557439087</v>
       </c>
       <c r="AP3">
-        <v>833.0761109020865</v>
+        <v>824.583835280682</v>
       </c>
       <c r="AQ3">
         <v>56.8624218172268</v>
       </c>
       <c r="AR3">
-        <v>42.49126534466478</v>
+        <v>45.22218219122466</v>
       </c>
       <c r="AS3">
-        <v>5.532847388817125</v>
+        <v>5.527442203458568</v>
       </c>
       <c r="AT3">
-        <v>4.409734222159909</v>
+        <v>4.407810921513979</v>
       </c>
       <c r="AU3">
         <v>61.15165496520426</v>
@@ -981,22 +981,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>413.4902098740756</v>
+        <v>398.1741506071476</v>
       </c>
       <c r="C5">
-        <v>68.51538084924498</v>
+        <v>43.74565464426878</v>
       </c>
       <c r="D5">
-        <v>6538.38245446515</v>
+        <v>6447.36629671723</v>
       </c>
       <c r="E5">
-        <v>209.6835760039729</v>
+        <v>188.0818522931034</v>
       </c>
       <c r="F5">
-        <v>374.0262391340003</v>
+        <v>365.2811543880227</v>
       </c>
       <c r="G5">
-        <v>12.60067356468474</v>
+        <v>12.97267417430036</v>
       </c>
       <c r="H5">
         <v>9.114944438413008</v>
@@ -1005,49 +1005,49 @@
         <v>94.22497703493447</v>
       </c>
       <c r="J5">
-        <v>40.00470122262512</v>
+        <v>36.26374780098146</v>
       </c>
       <c r="K5">
         <v>-1.913493609694627E-14</v>
       </c>
       <c r="L5">
-        <v>3630.728121019108</v>
+        <v>3562.132600660145</v>
       </c>
       <c r="M5">
-        <v>1220.800751640906</v>
+        <v>1144.613048808293</v>
       </c>
       <c r="N5">
-        <v>1657.196671974522</v>
+        <v>1600.257269733586</v>
       </c>
       <c r="O5">
-        <v>165.9859248676359</v>
+        <v>159.3951861253547</v>
       </c>
       <c r="P5">
         <v>19.3318941806601</v>
       </c>
       <c r="S5">
-        <v>0.0361522857166593</v>
+        <v>0.01807614285890483</v>
       </c>
       <c r="T5">
         <v>1.522509883925305</v>
       </c>
       <c r="U5">
-        <v>1.433229457110054</v>
+        <v>1.6772961649263</v>
       </c>
       <c r="V5">
-        <v>206.7065011580776</v>
+        <v>218.4175506253098</v>
       </c>
       <c r="W5">
-        <v>160.9533127470356</v>
+        <v>140.7454415356044</v>
       </c>
       <c r="Z5">
-        <v>-3.2409610753601E-14</v>
+        <v>-3.188324067919991E-14</v>
       </c>
       <c r="AA5">
-        <v>10.4491728470465</v>
+        <v>9.141095332209222</v>
       </c>
       <c r="AB5">
-        <v>9.365043096257695</v>
+        <v>12.97267417430036</v>
       </c>
       <c r="AC5">
         <v>2.616779913327972E-16</v>
@@ -1059,40 +1059,40 @@
         <v>12.04646692999412</v>
       </c>
       <c r="AH5">
-        <v>1429.207058482918</v>
+        <v>1394.705685725197</v>
       </c>
       <c r="AJ5">
-        <v>42.11441806601042</v>
+        <v>40.47899073954766</v>
       </c>
       <c r="AK5">
-        <v>1112.848383460228</v>
+        <v>1103.86844197715</v>
       </c>
       <c r="AL5">
-        <v>125.2594172616548</v>
+        <v>122.1390119905112</v>
       </c>
       <c r="AM5">
-        <v>72.64713520474027</v>
+        <v>56.39780457949308</v>
       </c>
       <c r="AN5">
-        <v>34.37591445852534</v>
+        <v>31.18591867135621</v>
       </c>
       <c r="AO5">
-        <v>452.2476249890937</v>
+        <v>383.611979231212</v>
       </c>
       <c r="AP5">
-        <v>648.4116849890066</v>
+        <v>611.2221751803496</v>
       </c>
       <c r="AQ5">
-        <v>12.78723930509401</v>
+        <v>14.61242778447267</v>
       </c>
       <c r="AR5">
-        <v>64.83804046233173</v>
+        <v>62.60868736080178</v>
       </c>
       <c r="AS5">
         <v>35.22086107921929</v>
       </c>
       <c r="AU5">
-        <v>205.6153018129811</v>
+        <v>196.7958367503846</v>
       </c>
       <c r="AV5">
         <v>1</v>
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>350.8147021768041</v>
+        <v>352.481087679455</v>
       </c>
       <c r="C6">
-        <v>32.55126664973344</v>
+        <v>33.12601676806608</v>
       </c>
       <c r="D6">
-        <v>5977.657846673373</v>
+        <v>5996.077022990088</v>
       </c>
       <c r="E6">
-        <v>103.625537640387</v>
+        <v>103.4738451701751</v>
       </c>
       <c r="F6">
-        <v>328.500579683218</v>
+        <v>329.9292869345614</v>
       </c>
       <c r="G6">
-        <v>17.51428034651915</v>
+        <v>17.61150656509352</v>
       </c>
       <c r="H6">
         <v>5.773593827775013</v>
@@ -1129,55 +1129,55 @@
         <v>209.9288514485036</v>
       </c>
       <c r="J6">
-        <v>28.71299786465505</v>
+        <v>29.61181043300375</v>
       </c>
       <c r="K6">
         <v>9.273740571928618E-15</v>
       </c>
       <c r="L6">
-        <v>4183.808065748052</v>
+        <v>4200.450257505004</v>
       </c>
       <c r="M6">
-        <v>638.8528061164935</v>
+        <v>641.1364493741479</v>
       </c>
       <c r="N6">
-        <v>1052.935800706844</v>
+        <v>1049.764736703452</v>
       </c>
       <c r="O6">
-        <v>72.28900907220351</v>
+        <v>71.87268982409263</v>
       </c>
       <c r="P6">
-        <v>11.2406980760256</v>
+        <v>11.42888621966115</v>
       </c>
       <c r="Q6">
         <v>2.890179627836936</v>
       </c>
       <c r="S6">
-        <v>7.526826259557396</v>
+        <v>7.769335078533388</v>
       </c>
       <c r="T6">
-        <v>12.0812979966611</v>
+        <v>12.21911559193452</v>
       </c>
       <c r="U6">
-        <v>7.419998755367478</v>
+        <v>7.624317419473417</v>
       </c>
       <c r="V6">
-        <v>109.5133235760338</v>
+        <v>109.8786918025557</v>
       </c>
       <c r="W6">
-        <v>166.8159015987111</v>
+        <v>167.0460833271223</v>
       </c>
       <c r="Z6">
-        <v>1.996489827249782E-14</v>
+        <v>1.902832981806715E-14</v>
       </c>
       <c r="AA6">
-        <v>15.17767611440873</v>
+        <v>15.33008449913827</v>
       </c>
       <c r="AB6">
-        <v>1.883380391419592</v>
+        <v>1.873304118367732</v>
       </c>
       <c r="AC6">
-        <v>-2.021347908133619E-16</v>
+        <v>-2.058199412660586E-16</v>
       </c>
       <c r="AD6">
         <v>0.1351699846782949</v>
@@ -1189,40 +1189,40 @@
         <v>0.1804582074521651</v>
       </c>
       <c r="AH6">
-        <v>2250.765603366898</v>
+        <v>2288.450384451317</v>
       </c>
       <c r="AJ6">
-        <v>45.79033585326558</v>
+        <v>46.09572236358496</v>
       </c>
       <c r="AK6">
-        <v>650.8421110089175</v>
+        <v>649.3149512023984</v>
       </c>
       <c r="AL6">
-        <v>148.861337306761</v>
+        <v>149.1982874328892</v>
       </c>
       <c r="AM6">
-        <v>808.6973780015492</v>
+        <v>806.6851672097411</v>
       </c>
       <c r="AN6">
         <v>32.10897424745097</v>
       </c>
       <c r="AO6">
-        <v>20.71018340332767</v>
+        <v>20.96198278256061</v>
       </c>
       <c r="AP6">
-        <v>493.7454685494223</v>
+        <v>499.8405740612762</v>
       </c>
       <c r="AQ6">
-        <v>40.43931626826672</v>
+        <v>40.79824387974647</v>
       </c>
       <c r="AR6">
-        <v>23.96999779371208</v>
+        <v>23.97479994985103</v>
       </c>
       <c r="AS6">
-        <v>9.211068043877695</v>
+        <v>9.211187063005351</v>
       </c>
       <c r="AT6">
-        <v>1.196950380553695</v>
+        <v>1.117301568007779</v>
       </c>
       <c r="AU6">
         <v>34.80163155365587</v>
@@ -1480,76 +1480,76 @@
         </is>
       </c>
       <c r="B9">
-        <v>545.7378921718523</v>
+        <v>549.2981223470333</v>
       </c>
       <c r="C9">
-        <v>132.6241103282866</v>
+        <v>136.8373080161188</v>
       </c>
       <c r="D9">
-        <v>6532.525897978622</v>
+        <v>6517.432708749699</v>
       </c>
       <c r="E9">
-        <v>349.4722130529491</v>
+        <v>365.6114772037478</v>
       </c>
       <c r="F9">
-        <v>474.6869633972992</v>
+        <v>483.9849966648892</v>
       </c>
       <c r="G9">
-        <v>53.01504975124379</v>
+        <v>53.08038858006523</v>
       </c>
       <c r="H9">
         <v>0.5835266396125148</v>
       </c>
       <c r="I9">
-        <v>138.5467381005542</v>
+        <v>138.1220880516457</v>
       </c>
       <c r="J9">
-        <v>89.8292738740452</v>
+        <v>91.49776464038524</v>
       </c>
       <c r="K9">
-        <v>8.430700958862792E-15</v>
+        <v>8.433448408210288E-15</v>
       </c>
       <c r="L9">
-        <v>3279.145877178284</v>
+        <v>3275.403100052637</v>
       </c>
       <c r="M9">
-        <v>2089.162812077871</v>
+        <v>2072.912872383251</v>
       </c>
       <c r="N9">
-        <v>1113.784550225981</v>
+        <v>1113.590140596729</v>
       </c>
       <c r="O9">
-        <v>206.8651069696682</v>
+        <v>205.7835205246351</v>
       </c>
       <c r="P9">
-        <v>94.2962349609916</v>
+        <v>99.42889528394028</v>
       </c>
       <c r="Q9">
         <v>0.769951680159711</v>
       </c>
       <c r="S9">
-        <v>35.6182305816803</v>
+        <v>35.40801053445175</v>
       </c>
       <c r="T9">
-        <v>58.23257376523413</v>
+        <v>58.71250559275737</v>
       </c>
       <c r="U9">
-        <v>44.80726372705811</v>
+        <v>45.70847705516775</v>
       </c>
       <c r="V9">
-        <v>230.4731929936596</v>
+        <v>231.5306820700607</v>
       </c>
       <c r="W9">
-        <v>156.8528275566048</v>
+        <v>156.8423622824711</v>
       </c>
       <c r="Z9">
-        <v>-2.05935471124951E-14</v>
+        <v>-2.108196179294709E-14</v>
       </c>
       <c r="AA9">
-        <v>17.35673148568832</v>
+        <v>17.3478338026256</v>
       </c>
       <c r="AB9">
-        <v>35.37594785442694</v>
+        <v>35.45732977171394</v>
       </c>
       <c r="AC9">
         <v>6.629936592600439E-17</v>
@@ -1567,43 +1567,43 @@
         <v>0.7783757766095443</v>
       </c>
       <c r="AH9">
-        <v>1932.526450400248</v>
+        <v>1931.699866238566</v>
       </c>
       <c r="AJ9">
-        <v>190.7531598062954</v>
+        <v>189.4986884685337</v>
       </c>
       <c r="AK9">
-        <v>540.7165715004402</v>
+        <v>540.0383913644503</v>
       </c>
       <c r="AL9">
-        <v>105.615641492929</v>
+        <v>105.5136678439629</v>
       </c>
       <c r="AM9">
-        <v>122.9130624559105</v>
+        <v>119.0603606897511</v>
       </c>
       <c r="AN9">
-        <v>21.23644201030928</v>
+        <v>21.26214276889795</v>
       </c>
       <c r="AO9">
-        <v>22.88135181265783</v>
+        <v>22.7865684012579</v>
       </c>
       <c r="AP9">
-        <v>1485.060486709982</v>
+        <v>1483.6711940687</v>
       </c>
       <c r="AQ9">
-        <v>154.4604296223639</v>
+        <v>154.4518904631188</v>
       </c>
       <c r="AR9">
-        <v>7.486446280991736</v>
+        <v>7.554550292046143</v>
       </c>
       <c r="AS9">
-        <v>34.15310754414983</v>
+        <v>33.94106557377049</v>
       </c>
       <c r="AT9">
-        <v>27.03334577114428</v>
+        <v>26.89676916436718</v>
       </c>
       <c r="AU9">
-        <v>221.7188168585555</v>
+        <v>220.2538001237685</v>
       </c>
       <c r="AV9">
         <v>1</v>
@@ -1619,10 +1619,10 @@
         <v>842.1912774017301</v>
       </c>
       <c r="C10">
-        <v>289.7960718981939</v>
+        <v>290.7962556545473</v>
       </c>
       <c r="D10">
-        <v>7779.616688941662</v>
+        <v>7824.881479716631</v>
       </c>
       <c r="E10">
         <v>348.589878111765</v>
@@ -1631,13 +1631,13 @@
         <v>802.0819527194764</v>
       </c>
       <c r="G10">
-        <v>40.13066415239069</v>
+        <v>40.07986222479403</v>
       </c>
       <c r="H10">
         <v>6.581133333333334</v>
       </c>
       <c r="I10">
-        <v>300.7929783136822</v>
+        <v>305.5469827134625</v>
       </c>
       <c r="J10">
         <v>56.95789947937525</v>
@@ -1649,7 +1649,7 @@
         <v>4154.19768983191</v>
       </c>
       <c r="M10">
-        <v>2482.627966682026</v>
+        <v>2491.556394500443</v>
       </c>
       <c r="N10">
         <v>838.8127846930881</v>
@@ -1670,7 +1670,7 @@
         <v>53.72012190240643</v>
       </c>
       <c r="T10">
-        <v>67.41809940752637</v>
+        <v>67.26801759480942</v>
       </c>
       <c r="U10">
         <v>149.0841759486314</v>
@@ -1679,13 +1679,13 @@
         <v>273.7698316520127</v>
       </c>
       <c r="W10">
-        <v>215.2670824283694</v>
+        <v>215.4485881220159</v>
       </c>
       <c r="Z10">
         <v>-1.674077104212465E-14</v>
       </c>
       <c r="AA10">
-        <v>20.96008654553387</v>
+        <v>20.85251623376623</v>
       </c>
       <c r="AB10">
         <v>14.39772070242397</v>
@@ -1706,7 +1706,7 @@
         <v>1.470845643041063</v>
       </c>
       <c r="AH10">
-        <v>2677.950561169912</v>
+        <v>2741.548801693074</v>
       </c>
       <c r="AJ10">
         <v>74.38103382072444</v>
@@ -1715,19 +1715,19 @@
         <v>541.6088506558663</v>
       </c>
       <c r="AL10">
-        <v>86.48370835929539</v>
+        <v>86.73649525355638</v>
       </c>
       <c r="AM10">
-        <v>36.55220325189012</v>
+        <v>36.72765145410592</v>
       </c>
       <c r="AN10">
-        <v>34.2899358226371</v>
+        <v>34.36837026539551</v>
       </c>
       <c r="AO10">
-        <v>268.4811393475919</v>
+        <v>270.5849748933834</v>
       </c>
       <c r="AP10">
-        <v>1866.184977532371</v>
+        <v>1876.79559223935</v>
       </c>
       <c r="AQ10">
         <v>167.1408913344304</v>
@@ -1736,13 +1736,13 @@
         <v>52.32232836905195</v>
       </c>
       <c r="AS10">
-        <v>23.12881464824928</v>
+        <v>22.95983163076797</v>
       </c>
       <c r="AT10">
         <v>7.992159680439119</v>
       </c>
       <c r="AU10">
-        <v>187.9808272846278</v>
+        <v>187.1305839314047</v>
       </c>
       <c r="AV10">
         <v>1</v>
@@ -1755,22 +1755,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>271.3840453074433</v>
+        <v>271.5784696484473</v>
       </c>
       <c r="C11">
         <v>48.3931805909126</v>
       </c>
       <c r="D11">
-        <v>6380.392780884303</v>
+        <v>6388.849777029231</v>
       </c>
       <c r="E11">
-        <v>92.96760541191735</v>
+        <v>93.71361697548815</v>
       </c>
       <c r="F11">
-        <v>253.4598772169168</v>
+        <v>253.5670255373588</v>
       </c>
       <c r="G11">
-        <v>4.678517422434368</v>
+        <v>4.587148526031998</v>
       </c>
       <c r="H11">
         <v>13.64586692122755</v>
@@ -1785,16 +1785,16 @@
         <v>1.073216045359242E-14</v>
       </c>
       <c r="L11">
-        <v>4648.701299174356</v>
+        <v>4649.805538169048</v>
       </c>
       <c r="M11">
-        <v>576.3831793276677</v>
+        <v>578.9442438812068</v>
       </c>
       <c r="N11">
-        <v>1039.309296363591</v>
+        <v>1036.59869045596</v>
       </c>
       <c r="O11">
-        <v>72.99974335281181</v>
+        <v>73.22981169188577</v>
       </c>
       <c r="P11">
         <v>9.079408226479135</v>
@@ -1803,28 +1803,28 @@
         <v>0.05101405951883867</v>
       </c>
       <c r="S11">
-        <v>2.932098995410381</v>
+        <v>2.963731019523886</v>
       </c>
       <c r="T11">
-        <v>1.161711366856404</v>
+        <v>1.151686856956018</v>
       </c>
       <c r="U11">
-        <v>4.840383921172424</v>
+        <v>4.887150980272834</v>
       </c>
       <c r="V11">
-        <v>82.05098882110903</v>
+        <v>82.19318062894372</v>
       </c>
       <c r="W11">
-        <v>142.0566528246388</v>
+        <v>141.7180301467265</v>
       </c>
       <c r="Z11">
-        <v>4.667283975587595E-16</v>
+        <v>-1.184478875777693E-15</v>
       </c>
       <c r="AA11">
         <v>3.283239521752231</v>
       </c>
       <c r="AB11">
-        <v>1.949293780337517</v>
+        <v>2.045687992376633</v>
       </c>
       <c r="AC11">
         <v>1.022648555459479E-16</v>
@@ -1842,31 +1842,31 @@
         <v>0.8486997964094021</v>
       </c>
       <c r="AH11">
-        <v>1917.480914938862</v>
+        <v>1922.770145910326</v>
       </c>
       <c r="AJ11">
-        <v>35.57198992090712</v>
+        <v>35.64493605789381</v>
       </c>
       <c r="AK11">
-        <v>790.3856025809274</v>
+        <v>789.1633843062193</v>
       </c>
       <c r="AL11">
-        <v>177.0625143272992</v>
+        <v>177.0163794749948</v>
       </c>
       <c r="AM11">
-        <v>1463.404233380704</v>
+        <v>1463.094656275588</v>
       </c>
       <c r="AN11">
-        <v>35.10222986111111</v>
+        <v>35.15311252946985</v>
       </c>
       <c r="AO11">
-        <v>47.50966262135946</v>
+        <v>49.25667809835592</v>
       </c>
       <c r="AP11">
-        <v>474.1814182334641</v>
+        <v>477.7072669588323</v>
       </c>
       <c r="AQ11">
-        <v>34.86353848617487</v>
+        <v>35.03344355979931</v>
       </c>
       <c r="AR11">
         <v>21.19330543933054</v>
@@ -1878,7 +1878,7 @@
         <v>0.2568273264275319</v>
       </c>
       <c r="AU11">
-        <v>15.98991570002732</v>
+        <v>15.8198728761286</v>
       </c>
       <c r="AV11">
         <v>1</v>
@@ -1894,19 +1894,19 @@
         <v>471.1061763022324</v>
       </c>
       <c r="C12">
-        <v>95.94523588817876</v>
+        <v>95.586116368029</v>
       </c>
       <c r="D12">
         <v>6336.80887034861</v>
       </c>
       <c r="E12">
-        <v>276.8376930099113</v>
+        <v>277.0701812249337</v>
       </c>
       <c r="F12">
         <v>429.8226617820846</v>
       </c>
       <c r="G12">
-        <v>33.31708564153057</v>
+        <v>33.31756974581526</v>
       </c>
       <c r="H12">
         <v>0.7983256145350909</v>
@@ -1924,16 +1924,16 @@
         <v>3773.589144505417</v>
       </c>
       <c r="M12">
-        <v>1555.481336717929</v>
+        <v>1554.221706341649</v>
       </c>
       <c r="N12">
-        <v>800.2877821363913</v>
+        <v>800.1033541142584</v>
       </c>
       <c r="O12">
-        <v>201.9386756019991</v>
+        <v>202.4792998239781</v>
       </c>
       <c r="P12">
-        <v>10.16855529318787</v>
+        <v>10.19370380078637</v>
       </c>
       <c r="Q12">
         <v>0.8076131687242798</v>
@@ -1945,25 +1945,25 @@
         <v>20.36292619089226</v>
       </c>
       <c r="T12">
-        <v>43.37962820891119</v>
+        <v>43.49920906679527</v>
       </c>
       <c r="U12">
-        <v>46.65965869660025</v>
+        <v>46.68175382841687</v>
       </c>
       <c r="V12">
-        <v>147.3945575447854</v>
+        <v>147.6024089443141</v>
       </c>
       <c r="W12">
-        <v>146.0594726017296</v>
+        <v>146.0333997785161</v>
       </c>
       <c r="Z12">
-        <v>1.171887676937133E-14</v>
+        <v>1.141917484903138E-14</v>
       </c>
       <c r="AA12">
         <v>11.95248037116346</v>
       </c>
       <c r="AB12">
-        <v>18.73349590373784</v>
+        <v>18.93649279161206</v>
       </c>
       <c r="AC12">
         <v>7.79019294734521E-17</v>
@@ -1984,40 +1984,40 @@
         <v>2641.514109957709</v>
       </c>
       <c r="AJ12">
-        <v>71.21413351100733</v>
+        <v>71.27843756283933</v>
       </c>
       <c r="AK12">
-        <v>613.7223436001248</v>
+        <v>613.3106758448059</v>
       </c>
       <c r="AL12">
-        <v>76.81353945154052</v>
+        <v>76.78203424956369</v>
       </c>
       <c r="AM12">
-        <v>31.96393883651415</v>
+        <v>31.73203786291205</v>
       </c>
       <c r="AN12">
-        <v>29.47392641874218</v>
+        <v>29.10599437489864</v>
       </c>
       <c r="AO12">
         <v>22.00650663008598</v>
       </c>
       <c r="AP12">
-        <v>930.3908059626074</v>
+        <v>930.1663274823857</v>
       </c>
       <c r="AQ12">
-        <v>186.8084611137948</v>
+        <v>186.8289259049835</v>
       </c>
       <c r="AR12">
-        <v>225.5150443932917</v>
+        <v>225.8552412701862</v>
       </c>
       <c r="AS12">
-        <v>10.64599470085754</v>
+        <v>10.68756679729248</v>
       </c>
       <c r="AT12">
         <v>1.939815386163185</v>
       </c>
       <c r="AU12">
-        <v>111.3117358384742</v>
+        <v>111.1532541987461</v>
       </c>
       <c r="AV12">
         <v>1</v>
@@ -2093,7 +2093,7 @@
         <v>404.1089236972443</v>
       </c>
       <c r="W13">
-        <v>343.5872743167828</v>
+        <v>344.9623400104059</v>
       </c>
       <c r="Z13">
         <v>5.109287186328324E-14</v>
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>1217.008394696597</v>
+        <v>1210.444867930172</v>
       </c>
       <c r="C14">
-        <v>307.8882896474652</v>
+        <v>307.6854554901282</v>
       </c>
       <c r="D14">
-        <v>8210.499215340811</v>
+        <v>8285.902551361933</v>
       </c>
       <c r="E14">
-        <v>469.5137284460254</v>
+        <v>474.1476874052526</v>
       </c>
       <c r="F14">
-        <v>1104.891272781036</v>
+        <v>1083.325346638378</v>
       </c>
       <c r="G14">
         <v>70.1917068912965</v>
@@ -2190,16 +2190,16 @@
         <v>235.2435950028662</v>
       </c>
       <c r="J14">
-        <v>92.71886059541902</v>
+        <v>91.79375824693686</v>
       </c>
       <c r="K14">
-        <v>7.106812019524112E-15</v>
+        <v>5.519581195315573E-15</v>
       </c>
       <c r="L14">
-        <v>3201.520331169863</v>
+        <v>3244.303130229067</v>
       </c>
       <c r="M14">
-        <v>3698.514659423688</v>
+        <v>3763.89708986257</v>
       </c>
       <c r="N14">
         <v>1227.665646941396</v>
@@ -2208,31 +2208,31 @@
         <v>274.5538544478901</v>
       </c>
       <c r="P14">
-        <v>93.29317893164614</v>
+        <v>89.48052764045616</v>
       </c>
       <c r="Q14">
         <v>1.248993123548431</v>
       </c>
       <c r="S14">
-        <v>79.29836408919209</v>
+        <v>79.64054426790221</v>
       </c>
       <c r="T14">
-        <v>113.4173302771076</v>
+        <v>111.9288060707105</v>
       </c>
       <c r="U14">
-        <v>202.6881136468232</v>
+        <v>208.9067242959009</v>
       </c>
       <c r="V14">
         <v>391.0904795120989</v>
       </c>
       <c r="W14">
-        <v>328.808070616857</v>
+        <v>328.1510511136108</v>
       </c>
       <c r="Z14">
-        <v>1.262599526867625E-13</v>
+        <v>1.190543601434479E-13</v>
       </c>
       <c r="AA14">
-        <v>34.08089729263259</v>
+        <v>33.42666687937166</v>
       </c>
       <c r="AB14">
         <v>27.67552092071268</v>
@@ -2253,16 +2253,16 @@
         <v>0.2694859428032323</v>
       </c>
       <c r="AH14">
-        <v>1936.623859782474</v>
+        <v>1959.044199174394</v>
       </c>
       <c r="AJ14">
-        <v>60.23782392091884</v>
+        <v>61.19819055240928</v>
       </c>
       <c r="AK14">
-        <v>521.765263905949</v>
+        <v>532.4654323557518</v>
       </c>
       <c r="AL14">
-        <v>106.5576396496167</v>
+        <v>106.8587920107782</v>
       </c>
       <c r="AM14">
         <v>52.49921122250679</v>
@@ -2271,25 +2271,25 @@
         <v>24.05868922444462</v>
       </c>
       <c r="AO14">
-        <v>374.5291086451645</v>
+        <v>368.3538232658051</v>
       </c>
       <c r="AP14">
         <v>2873.440187058914</v>
       </c>
       <c r="AQ14">
-        <v>204.5406245584257</v>
+        <v>204.2558616193948</v>
       </c>
       <c r="AR14">
-        <v>201.3825451129178</v>
+        <v>207.0920961062994</v>
       </c>
       <c r="AS14">
-        <v>10.42676118218669</v>
+        <v>10.43109786579504</v>
       </c>
       <c r="AT14">
-        <v>45.66567917605976</v>
+        <v>48.58217384197194</v>
       </c>
       <c r="AU14">
-        <v>348.7305918461557</v>
+        <v>353.2820006435614</v>
       </c>
       <c r="AV14">
         <v>1</v>
@@ -2302,76 +2302,76 @@
         </is>
       </c>
       <c r="B15">
-        <v>357.7644610175856</v>
+        <v>365.049264441367</v>
       </c>
       <c r="C15">
-        <v>64.30693912341638</v>
+        <v>65.505932730225</v>
       </c>
       <c r="D15">
-        <v>5594.847214903799</v>
+        <v>5604.611537542254</v>
       </c>
       <c r="E15">
-        <v>91.20587493110777</v>
+        <v>90.63738072607663</v>
       </c>
       <c r="F15">
-        <v>318.5760725663177</v>
+        <v>326.2253602976372</v>
       </c>
       <c r="G15">
-        <v>20.64240360568746</v>
+        <v>20.58072205602393</v>
       </c>
       <c r="H15">
         <v>21.47982135996927</v>
       </c>
       <c r="I15">
-        <v>182.6611231723595</v>
+        <v>188.5818413368514</v>
       </c>
       <c r="J15">
-        <v>50.49470635537054</v>
+        <v>50.89448105948505</v>
       </c>
       <c r="K15">
-        <v>-5.915799143886172E-15</v>
+        <v>-7.905641999438719E-15</v>
       </c>
       <c r="L15">
-        <v>3665.14855503969</v>
+        <v>3675.387423385743</v>
       </c>
       <c r="M15">
-        <v>826.9730848214308</v>
+        <v>802.163744530035</v>
       </c>
       <c r="N15">
-        <v>1000.978551705484</v>
+        <v>1003.499516651374</v>
       </c>
       <c r="O15">
-        <v>72.0438035688133</v>
+        <v>71.27599320385505</v>
       </c>
       <c r="P15">
-        <v>2.196935458167331</v>
+        <v>2.385195043952132</v>
       </c>
       <c r="S15">
-        <v>3.312861259538954</v>
+        <v>3.157449668052601</v>
       </c>
       <c r="T15">
         <v>6.677878086091871</v>
       </c>
       <c r="U15">
-        <v>8.302001048492793</v>
+        <v>8.502374431311583</v>
       </c>
       <c r="V15">
-        <v>105.1417882013693</v>
+        <v>104.7895525727069</v>
       </c>
       <c r="W15">
-        <v>189.9491216044831</v>
+        <v>189.9893961342991</v>
       </c>
       <c r="Z15">
-        <v>1.556979026707701E-14</v>
+        <v>1.509045587230991E-14</v>
       </c>
       <c r="AA15">
-        <v>11.1055152471747</v>
+        <v>10.68821964086377</v>
       </c>
       <c r="AB15">
-        <v>5.194462144308943</v>
+        <v>5.121255939866947</v>
       </c>
       <c r="AC15">
-        <v>2.063984345337407E-16</v>
+        <v>1.658916435897729E-16</v>
       </c>
       <c r="AD15">
         <v>1.03155306216269</v>
@@ -2386,43 +2386,43 @@
         <v>0.6947002930978334</v>
       </c>
       <c r="AH15">
-        <v>1348.027185219588</v>
+        <v>1335.205546996492</v>
       </c>
       <c r="AJ15">
-        <v>29.8412622664133</v>
+        <v>29.32846658359021</v>
       </c>
       <c r="AK15">
-        <v>655.9368057105571</v>
+        <v>646.5676917529272</v>
       </c>
       <c r="AL15">
-        <v>173.8675610250219</v>
+        <v>174.0422055936752</v>
       </c>
       <c r="AM15">
-        <v>1084.721449923174</v>
+        <v>1091.144081238708</v>
       </c>
       <c r="AN15">
-        <v>25.77257946896036</v>
+        <v>25.51992696844622</v>
       </c>
       <c r="AO15">
-        <v>69.57830254773263</v>
+        <v>67.83173156188727</v>
       </c>
       <c r="AP15">
-        <v>625.7126515469354</v>
+        <v>619.2841822262548</v>
       </c>
       <c r="AQ15">
-        <v>37.34626431124438</v>
+        <v>37.83599604810266</v>
       </c>
       <c r="AR15">
-        <v>20.75738817746239</v>
+        <v>21.70605015460918</v>
       </c>
       <c r="AS15">
-        <v>3.864291192817406</v>
+        <v>3.852976343627308</v>
       </c>
       <c r="AT15">
         <v>5.264389053214085</v>
       </c>
       <c r="AU15">
-        <v>93.99051634296788</v>
+        <v>92.83800262123192</v>
       </c>
       <c r="AV15">
         <v>1</v>
@@ -2435,46 +2435,46 @@
         </is>
       </c>
       <c r="B16">
-        <v>291.4390704453126</v>
+        <v>293.0162917761922</v>
       </c>
       <c r="C16">
-        <v>80.10491253916459</v>
+        <v>78.5603125884017</v>
       </c>
       <c r="D16">
-        <v>6996.820680797216</v>
+        <v>7011.047009966777</v>
       </c>
       <c r="E16">
-        <v>171.184136872569</v>
+        <v>171.7768213058419</v>
       </c>
       <c r="F16">
-        <v>282.2641288229636</v>
+        <v>283.3909717114569</v>
       </c>
       <c r="G16">
-        <v>4.245579507162223</v>
+        <v>4.251135005973715</v>
       </c>
       <c r="H16">
         <v>53.79397032866993</v>
       </c>
       <c r="I16">
-        <v>180.7882249916112</v>
+        <v>181.5534443910403</v>
       </c>
       <c r="J16">
-        <v>42.39975384988481</v>
+        <v>42.15599915801532</v>
       </c>
       <c r="K16">
         <v>1.627144785433848E-14</v>
       </c>
       <c r="L16">
-        <v>4938.097759055293</v>
+        <v>4944.498821336392</v>
       </c>
       <c r="M16">
-        <v>606.8969612801482</v>
+        <v>610.672728056137</v>
       </c>
       <c r="N16">
-        <v>1245.567120769511</v>
+        <v>1251.135344978167</v>
       </c>
       <c r="O16">
-        <v>146.0338744724025</v>
+        <v>147.8030434782609</v>
       </c>
       <c r="P16">
         <v>3.051979000954502</v>
@@ -2483,28 +2483,28 @@
         <v>33.71763317599461</v>
       </c>
       <c r="S16">
-        <v>17.87985999411199</v>
+        <v>17.55570483670892</v>
       </c>
       <c r="T16">
-        <v>8.024679851184649</v>
+        <v>7.958107090916451</v>
       </c>
       <c r="U16">
         <v>5.799686100866053</v>
       </c>
       <c r="V16">
-        <v>76.63342910560525</v>
+        <v>76.26146191646193</v>
       </c>
       <c r="W16">
-        <v>179.1273568510987</v>
+        <v>179.8604874401914</v>
       </c>
       <c r="Z16">
-        <v>-2.03558877123509E-14</v>
+        <v>-2.079981912244289E-14</v>
       </c>
       <c r="AA16">
-        <v>2.879939694927279</v>
+        <v>2.788031994047619</v>
       </c>
       <c r="AB16">
-        <v>1.995154721626862</v>
+        <v>1.93417953535261</v>
       </c>
       <c r="AC16">
         <v>9.530354110780047E-17</v>
@@ -2516,43 +2516,43 @@
         <v>2.437539222821127</v>
       </c>
       <c r="AH16">
-        <v>2875.304034390516</v>
+        <v>2905.959279636983</v>
       </c>
       <c r="AJ16">
-        <v>56.73081840255633</v>
+        <v>57.31567220052083</v>
       </c>
       <c r="AK16">
-        <v>950.3996894883813</v>
+        <v>950.0647544642858</v>
       </c>
       <c r="AL16">
-        <v>145.9637409928347</v>
+        <v>146.1036823966066</v>
       </c>
       <c r="AM16">
-        <v>530.4818836437121</v>
+        <v>532.3398642714571</v>
       </c>
       <c r="AN16">
-        <v>56.70973700887199</v>
+        <v>56.65212465231518</v>
       </c>
       <c r="AO16">
-        <v>19.65829846993825</v>
+        <v>19.77858241203185</v>
       </c>
       <c r="AP16">
-        <v>482.3446206170599</v>
+        <v>482.3617395609836</v>
       </c>
       <c r="AQ16">
-        <v>29.57987938026213</v>
+        <v>29.77092303268475</v>
       </c>
       <c r="AR16">
-        <v>7.682049072411729</v>
+        <v>7.586612700747601</v>
       </c>
       <c r="AS16">
-        <v>6.263969477183439</v>
+        <v>6.304156136556369</v>
       </c>
       <c r="AT16">
         <v>0.5393222515324018</v>
       </c>
       <c r="AU16">
-        <v>42.31083223451127</v>
+        <v>42.36204836415362</v>
       </c>
       <c r="AV16">
         <v>1</v>
@@ -2695,73 +2695,73 @@
         </is>
       </c>
       <c r="B18">
-        <v>321.558614616558</v>
+        <v>321.3788232848546</v>
       </c>
       <c r="C18">
-        <v>76.79050534878537</v>
+        <v>75.37835776302418</v>
       </c>
       <c r="D18">
-        <v>7344.553798245614</v>
+        <v>7358.862816338235</v>
       </c>
       <c r="E18">
-        <v>162.7166963482641</v>
+        <v>162.1724347989076</v>
       </c>
       <c r="F18">
-        <v>308.0231876758999</v>
+        <v>307.6842273727403</v>
       </c>
       <c r="G18">
-        <v>3.076966858789625</v>
+        <v>3.102628166236918</v>
       </c>
       <c r="H18">
         <v>1.465901960784314</v>
       </c>
       <c r="I18">
-        <v>192.1125416289201</v>
+        <v>193.2695890892063</v>
       </c>
       <c r="J18">
-        <v>62.13437882607131</v>
+        <v>61.96596182682876</v>
       </c>
       <c r="K18">
         <v>1.002715950275063E-14</v>
       </c>
       <c r="L18">
-        <v>5410.822688450339</v>
+        <v>5437.52676506927</v>
       </c>
       <c r="M18">
-        <v>612.6089078947368</v>
+        <v>615.1441567053653</v>
       </c>
       <c r="N18">
-        <v>1192.041047060297</v>
+        <v>1190.163223511674</v>
       </c>
       <c r="O18">
-        <v>132.4650766580534</v>
+        <v>132.2281050047097</v>
       </c>
       <c r="P18">
-        <v>5.05320796460177</v>
+        <v>5.066235169618905</v>
       </c>
       <c r="S18">
-        <v>8.179900921429818</v>
+        <v>7.713892134656915</v>
       </c>
       <c r="T18">
-        <v>2.886544113257357</v>
+        <v>2.857364211072413</v>
       </c>
       <c r="U18">
         <v>2.444430619421152</v>
       </c>
       <c r="V18">
-        <v>110.699778597786</v>
+        <v>110.7468147647315</v>
       </c>
       <c r="W18">
-        <v>182.9373819823209</v>
+        <v>179.6112328991471</v>
       </c>
       <c r="Z18">
-        <v>-1.130913888405465E-14</v>
+        <v>-1.076275337003049E-14</v>
       </c>
       <c r="AA18">
-        <v>1.192546403712297</v>
+        <v>1.176563339903243</v>
       </c>
       <c r="AB18">
-        <v>1.582942839963171</v>
+        <v>1.64272304713637</v>
       </c>
       <c r="AC18">
         <v>3.395429935321545E-17</v>
@@ -2776,43 +2776,43 @@
         <v>0.2359013659281808</v>
       </c>
       <c r="AH18">
-        <v>2753.727165225901</v>
+        <v>2803.547804307708</v>
       </c>
       <c r="AJ18">
-        <v>48.79836248694467</v>
+        <v>49.55596049046321</v>
       </c>
       <c r="AK18">
-        <v>1034.992305270732</v>
+        <v>1035.027374036281</v>
       </c>
       <c r="AL18">
-        <v>167.6571106442577</v>
+        <v>167.9765291367977</v>
       </c>
       <c r="AM18">
-        <v>1030.696044189505</v>
+        <v>1029.777160996023</v>
       </c>
       <c r="AN18">
-        <v>88.5120352708787</v>
+        <v>88.64355233447448</v>
       </c>
       <c r="AO18">
-        <v>28.34323659306002</v>
+        <v>28.34175074081208</v>
       </c>
       <c r="AP18">
-        <v>523.5928768750928</v>
+        <v>527.5751469798095</v>
       </c>
       <c r="AQ18">
-        <v>25.77509433962264</v>
+        <v>25.58035498411385</v>
       </c>
       <c r="AR18">
-        <v>11.28688509874327</v>
+        <v>11.69940766256815</v>
       </c>
       <c r="AS18">
-        <v>5.29785731104309</v>
+        <v>5.288932419196866</v>
       </c>
       <c r="AT18">
         <v>0.1449608633696535</v>
       </c>
       <c r="AU18">
-        <v>28.35798620094873</v>
+        <v>28.55201289144608</v>
       </c>
       <c r="AV18">
         <v>1</v>
@@ -2825,85 +2825,88 @@
         </is>
       </c>
       <c r="B19">
-        <v>831.1411416349174</v>
+        <v>829.4855329080674</v>
       </c>
       <c r="C19">
-        <v>152.9423312368973</v>
+        <v>152.2037440182142</v>
       </c>
       <c r="D19">
-        <v>6739.003798312177</v>
+        <v>6794.649701330532</v>
       </c>
       <c r="E19">
-        <v>579.8809178338358</v>
+        <v>580.0706872561648</v>
       </c>
       <c r="F19">
-        <v>748.2371907687199</v>
+        <v>747.9642106595022</v>
       </c>
       <c r="G19">
-        <v>78.4037210372871</v>
+        <v>77.87194500940805</v>
       </c>
       <c r="H19">
-        <v>1.114156500116559</v>
+        <v>1.083875587820746</v>
       </c>
       <c r="I19">
         <v>290.7155719199224</v>
       </c>
       <c r="J19">
-        <v>92.58359732217734</v>
+        <v>92.49063409424643</v>
       </c>
       <c r="K19">
-        <v>9.01885046691469E-15</v>
+        <v>1.125286206995833E-14</v>
       </c>
       <c r="L19">
-        <v>3530.148246852933</v>
+        <v>3545.531069450581</v>
       </c>
       <c r="M19">
-        <v>2047.749087503746</v>
+        <v>2042.615196069754</v>
       </c>
       <c r="N19">
-        <v>880.6605726330586</v>
+        <v>882.2154826089318</v>
       </c>
       <c r="O19">
-        <v>380.7239411893422</v>
+        <v>381.5012748171368</v>
       </c>
       <c r="P19">
         <v>14.8962916975102</v>
       </c>
       <c r="Q19">
-        <v>0.7121344119477288</v>
+        <v>0.660372508109745</v>
       </c>
       <c r="R19">
         <v>0.4830715219652364</v>
       </c>
       <c r="S19">
-        <v>57.43528956865308</v>
+        <v>57.10959851932287</v>
       </c>
       <c r="T19">
-        <v>122.0721735045412</v>
+        <v>120.3850833685108</v>
       </c>
       <c r="U19">
-        <v>104.0514904924074</v>
+        <v>104.2967388488626</v>
       </c>
       <c r="V19">
-        <v>199.6363684020246</v>
+        <v>199.2262237975066</v>
       </c>
       <c r="W19">
-        <v>267.6942153144239</v>
+        <v>268.7204671012183</v>
       </c>
       <c r="Z19">
-        <v>3.771452881734343E-14</v>
+        <v>3.735350238562355E-14</v>
       </c>
       <c r="AA19">
-        <v>20.97509145475578</v>
+        <v>21.04575470466943</v>
       </c>
       <c r="AB19">
-        <v>55.96742761701785</v>
+        <v>54.61515075885329</v>
       </c>
       <c r="AC19">
-        <v>-6.519675281526367E-16</v>
+        <v>3.166764281939165E-16</v>
       </c>
       <c r="AD19">
-        <v>1.058232020667504</v>
+        <v>1.009484602917342</v>
+      </c>
+      <c r="AE19">
+        <v>9.70717674858223</v>
       </c>
       <c r="AF19">
         <v>0.6118350421243341</v>
@@ -2912,43 +2915,43 @@
         <v>0.3103345454545466</v>
       </c>
       <c r="AH19">
-        <v>2632.805727536407</v>
+        <v>2640.941835654596</v>
       </c>
       <c r="AJ19">
-        <v>55.45168360744879</v>
+        <v>56.552177877429</v>
       </c>
       <c r="AK19">
-        <v>405.4835174941225</v>
+        <v>405.3171321747342</v>
       </c>
       <c r="AL19">
-        <v>86.90551884667367</v>
+        <v>86.98162599250173</v>
       </c>
       <c r="AM19">
-        <v>41.32278752436648</v>
+        <v>40.73331525316469</v>
       </c>
       <c r="AN19">
-        <v>25.24876890551309</v>
+        <v>25.36632053577349</v>
       </c>
       <c r="AO19">
-        <v>131.9517217753949</v>
+        <v>132.9133371764807</v>
       </c>
       <c r="AP19">
-        <v>1558.851002938667</v>
+        <v>1556.629935772761</v>
       </c>
       <c r="AQ19">
-        <v>220.1558575279708</v>
+        <v>219.2288405077654</v>
       </c>
       <c r="AR19">
-        <v>62.70764761961508</v>
+        <v>63.22454322501533</v>
       </c>
       <c r="AS19">
-        <v>44.008586333302</v>
+        <v>43.95002735121281</v>
       </c>
       <c r="AT19">
-        <v>1.421895635673624</v>
+        <v>1.419025869197149</v>
       </c>
       <c r="AU19">
-        <v>120.0037066814528</v>
+        <v>121.2159586344712</v>
       </c>
       <c r="AV19">
         <v>1</v>
@@ -2973,7 +2976,7 @@
         <v>378.530268288201</v>
       </c>
       <c r="F20">
-        <v>795.1421101700079</v>
+        <v>795.8704575476386</v>
       </c>
       <c r="G20">
         <v>74.30895041198855</v>
@@ -2982,7 +2985,7 @@
         <v>9.326571642910727</v>
       </c>
       <c r="I20">
-        <v>252.8451762110522</v>
+        <v>253.2489088300924</v>
       </c>
       <c r="J20">
         <v>81.26611483277996</v>
@@ -3000,7 +3003,7 @@
         <v>902.7588777680462</v>
       </c>
       <c r="O20">
-        <v>252.4300090094362</v>
+        <v>257.6800438269303</v>
       </c>
       <c r="P20">
         <v>9.093369310152365</v>
@@ -3012,7 +3015,7 @@
         <v>0.4500406805860108</v>
       </c>
       <c r="S20">
-        <v>84.73842292239345</v>
+        <v>85.38551526202301</v>
       </c>
       <c r="T20">
         <v>176.7574058280028</v>
@@ -3021,16 +3024,16 @@
         <v>34.26633079900855</v>
       </c>
       <c r="V20">
-        <v>300.8105811423964</v>
+        <v>302.0169595008635</v>
       </c>
       <c r="W20">
-        <v>284.1735439362736</v>
+        <v>284.4338002296211</v>
       </c>
       <c r="Z20">
-        <v>2.497931604560911E-14</v>
+        <v>1.769752345151047E-14</v>
       </c>
       <c r="AA20">
-        <v>24.45198143187045</v>
+        <v>24.56054658245745</v>
       </c>
       <c r="AB20">
         <v>46.46207692312383</v>
@@ -3051,7 +3054,7 @@
         <v>1398.226863494702</v>
       </c>
       <c r="AK20">
-        <v>725.489685459114</v>
+        <v>719.5215464961666</v>
       </c>
       <c r="AL20">
         <v>93.31445792487625</v>
@@ -3075,7 +3078,7 @@
         <v>69.17810064424573</v>
       </c>
       <c r="AS20">
-        <v>12.6261611504851</v>
+        <v>12.65825112034934</v>
       </c>
       <c r="AT20">
         <v>168.5801743586084</v>
@@ -3224,22 +3227,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>638.6891898093417</v>
+        <v>651.6748020152024</v>
       </c>
       <c r="C22">
-        <v>150.9686019679605</v>
+        <v>186.6791251495875</v>
       </c>
       <c r="D22">
-        <v>6486.945039533327</v>
+        <v>6384.226143463397</v>
       </c>
       <c r="E22">
-        <v>619.9970199744042</v>
+        <v>615.8500992708424</v>
       </c>
       <c r="F22">
-        <v>556.9778057321757</v>
+        <v>557.852160900317</v>
       </c>
       <c r="G22">
-        <v>79.21314675951569</v>
+        <v>79.71305851231341</v>
       </c>
       <c r="H22">
         <v>7.393030927835052</v>
@@ -3248,52 +3251,52 @@
         <v>203.677351311801</v>
       </c>
       <c r="J22">
-        <v>47.57662715714164</v>
+        <v>48.10658846944435</v>
       </c>
       <c r="K22">
         <v>2.452554866325957E-15</v>
       </c>
       <c r="L22">
-        <v>2884.141888816832</v>
+        <v>2872.65762339319</v>
       </c>
       <c r="M22">
-        <v>2374.060967217833</v>
+        <v>2364.98568848574</v>
       </c>
       <c r="N22">
-        <v>1117.82554002121</v>
+        <v>1109.801537462103</v>
       </c>
       <c r="O22">
-        <v>554.7411823598095</v>
+        <v>544.8477813862855</v>
       </c>
       <c r="P22">
-        <v>13.40371279393796</v>
+        <v>14.31936575117228</v>
       </c>
       <c r="Q22">
         <v>0.008253024506255816</v>
       </c>
       <c r="S22">
-        <v>46.07677786843765</v>
+        <v>47.75434828776249</v>
       </c>
       <c r="T22">
-        <v>71.48853168715587</v>
+        <v>73.54359520400858</v>
       </c>
       <c r="U22">
-        <v>57.40595109536271</v>
+        <v>57.11619577820486</v>
       </c>
       <c r="V22">
-        <v>160.1128887958049</v>
+        <v>157.6922477686834</v>
       </c>
       <c r="W22">
-        <v>234.0157372262774</v>
+        <v>234.2572652068127</v>
       </c>
       <c r="Z22">
-        <v>-2.659003360762531E-14</v>
+        <v>-2.745746471463198E-14</v>
       </c>
       <c r="AA22">
-        <v>17.36832762194483</v>
+        <v>17.68066239193908</v>
       </c>
       <c r="AB22">
-        <v>64.104336935167</v>
+        <v>64.32895469923935</v>
       </c>
       <c r="AC22">
         <v>-2.121270441452894E-15</v>
@@ -3308,43 +3311,43 @@
         <v>0.003866172025281671</v>
       </c>
       <c r="AH22">
-        <v>1816.00229332501</v>
+        <v>1804.3208117506</v>
       </c>
       <c r="AJ22">
-        <v>40.51471405928525</v>
+        <v>39.93414588012767</v>
       </c>
       <c r="AK22">
-        <v>721.25747719356</v>
+        <v>718.0784921000154</v>
       </c>
       <c r="AL22">
-        <v>92.83584864012353</v>
+        <v>91.37257955936353</v>
       </c>
       <c r="AM22">
-        <v>26.82640379784006</v>
+        <v>27.36416415427884</v>
       </c>
       <c r="AN22">
-        <v>23.85031912715728</v>
+        <v>23.60338726812127</v>
       </c>
       <c r="AO22">
-        <v>76.31042567803429</v>
+        <v>78.48432361516056</v>
       </c>
       <c r="AP22">
-        <v>1742.589515567835</v>
+        <v>1742.057793187348</v>
       </c>
       <c r="AQ22">
-        <v>150.5866521995416</v>
+        <v>150.9050626822157</v>
       </c>
       <c r="AR22">
-        <v>54.11215648027741</v>
+        <v>59.58777434828825</v>
       </c>
       <c r="AS22">
-        <v>12.87079444658696</v>
+        <v>12.38587170166198</v>
       </c>
       <c r="AT22">
         <v>7.371706646819717</v>
       </c>
       <c r="AU22">
-        <v>335.1322091530582</v>
+        <v>332.2377596531077</v>
       </c>
       <c r="AV22">
         <v>1</v>
@@ -3357,22 +3360,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>405.9330603392818</v>
+        <v>425.6495634788404</v>
       </c>
       <c r="C23">
         <v>33.43016992961698</v>
       </c>
       <c r="D23">
-        <v>5328.321989900858</v>
+        <v>4975.777597384134</v>
       </c>
       <c r="E23">
-        <v>161.2899871266379</v>
+        <v>154.7064210010415</v>
       </c>
       <c r="F23">
-        <v>378.9341546061154</v>
+        <v>408.1368560479841</v>
       </c>
       <c r="G23">
-        <v>8.314697869237811</v>
+        <v>8.342652301834544</v>
       </c>
       <c r="H23">
         <v>37.97439035998615</v>
@@ -3387,22 +3390,22 @@
         <v>-1.534692806646624E-14</v>
       </c>
       <c r="L23">
-        <v>2455.749916885717</v>
+        <v>2434.23419898303</v>
       </c>
       <c r="M23">
-        <v>1171.809780823175</v>
+        <v>1206.987039147216</v>
       </c>
       <c r="N23">
-        <v>1654.247831668484</v>
+        <v>1647.12532640208</v>
       </c>
       <c r="O23">
-        <v>145.4503925535566</v>
+        <v>141.7184264720584</v>
       </c>
       <c r="P23">
         <v>4.84756237679643</v>
       </c>
       <c r="S23">
-        <v>11.70025905942798</v>
+        <v>12.26915735388534</v>
       </c>
       <c r="T23">
         <v>14.93405394990366</v>
@@ -3411,16 +3414,16 @@
         <v>19.02889005259758</v>
       </c>
       <c r="V23">
-        <v>240.4124573779354</v>
+        <v>255.9038083416087</v>
       </c>
       <c r="W23">
-        <v>114.790159407184</v>
+        <v>115.8315017533883</v>
       </c>
       <c r="Z23">
         <v>2.558578501690875E-15</v>
       </c>
       <c r="AA23">
-        <v>5.455019706168157</v>
+        <v>5.721727324424225</v>
       </c>
       <c r="AB23">
         <v>3.872188906195916</v>
@@ -3432,31 +3435,31 @@
         <v>37.97439035998615</v>
       </c>
       <c r="AH23">
-        <v>747.2993643579418</v>
+        <v>753.6834393187527</v>
       </c>
       <c r="AJ23">
-        <v>13.19621665544673</v>
+        <v>13.23689334068492</v>
       </c>
       <c r="AK23">
-        <v>901.4335826701729</v>
+        <v>908.9925841386205</v>
       </c>
       <c r="AL23">
-        <v>125.6519104027669</v>
+        <v>122.7056495134918</v>
       </c>
       <c r="AM23">
         <v>53.30954009433962</v>
       </c>
       <c r="AN23">
-        <v>33.52521031496038</v>
+        <v>37.53077130429455</v>
       </c>
       <c r="AO23">
-        <v>198.2237839552116</v>
+        <v>163.7916441875401</v>
       </c>
       <c r="AP23">
-        <v>805.4523550712095</v>
+        <v>814.9076806107249</v>
       </c>
       <c r="AQ23">
-        <v>15.04027135070786</v>
+        <v>15.15720747252747</v>
       </c>
       <c r="AR23">
         <v>13.19459932804416</v>
@@ -3465,7 +3468,7 @@
         <v>3.814679993240846</v>
       </c>
       <c r="AU23">
-        <v>213.4158076003532</v>
+        <v>243.467528550149</v>
       </c>
       <c r="AV23">
         <v>1</v>
@@ -3478,49 +3481,49 @@
         </is>
       </c>
       <c r="B24">
-        <v>890.2795900229357</v>
+        <v>893.3273148648582</v>
       </c>
       <c r="C24">
-        <v>249.9109374925584</v>
+        <v>250.3049692808095</v>
       </c>
       <c r="D24">
-        <v>7853.07884850879</v>
+        <v>7869.068362242161</v>
       </c>
       <c r="E24">
-        <v>934.4858766834749</v>
+        <v>942.0493927541172</v>
       </c>
       <c r="F24">
-        <v>806.5173493975905</v>
+        <v>807.6928648701052</v>
       </c>
       <c r="G24">
-        <v>76.50437958209022</v>
+        <v>76.58843625802507</v>
       </c>
       <c r="H24">
-        <v>5.048908948194662</v>
+        <v>5.108446018489273</v>
       </c>
       <c r="I24">
-        <v>242.5234915183682</v>
+        <v>242.6033333333334</v>
       </c>
       <c r="J24">
-        <v>48.83458032252312</v>
+        <v>48.9878212535014</v>
       </c>
       <c r="K24">
         <v>5.993375299986348E-15</v>
       </c>
       <c r="L24">
-        <v>4231.108964536635</v>
+        <v>4236.620449012324</v>
       </c>
       <c r="M24">
-        <v>2453.696065002902</v>
+        <v>2455.642092686636</v>
       </c>
       <c r="N24">
-        <v>1049.334409769335</v>
+        <v>1051.359955559431</v>
       </c>
       <c r="O24">
-        <v>713.2220058543726</v>
+        <v>716.6339811880558</v>
       </c>
       <c r="P24">
-        <v>38.45028534519531</v>
+        <v>38.51463290724353</v>
       </c>
       <c r="Q24">
         <v>1.758999341672153</v>
@@ -3529,34 +3532,34 @@
         <v>1.121639385784391</v>
       </c>
       <c r="S24">
-        <v>67.56942252344214</v>
+        <v>67.73230939793059</v>
       </c>
       <c r="T24">
-        <v>155.8050776557954</v>
+        <v>155.8916840448554</v>
       </c>
       <c r="U24">
-        <v>89.21995019768856</v>
+        <v>89.29018019267806</v>
       </c>
       <c r="V24">
-        <v>211.3168177063019</v>
+        <v>211.9624386677498</v>
       </c>
       <c r="W24">
-        <v>267.2991257946267</v>
+        <v>267.7268080967225</v>
       </c>
       <c r="Z24">
         <v>3.265964983221625E-14</v>
       </c>
       <c r="AA24">
-        <v>21.89121191629795</v>
+        <v>21.97496387836249</v>
       </c>
       <c r="AB24">
-        <v>49.82049445005045</v>
+        <v>49.86251702446894</v>
       </c>
       <c r="AC24">
         <v>1.016952704181433E-15</v>
       </c>
       <c r="AD24">
-        <v>5.048908948194662</v>
+        <v>5.108446018489273</v>
       </c>
       <c r="AE24">
         <v>0.2333747907199235</v>
@@ -3568,34 +3571,34 @@
         <v>0.255847569760894</v>
       </c>
       <c r="AH24">
-        <v>3432.443285974499</v>
+        <v>3437.77414070331</v>
       </c>
       <c r="AJ24">
-        <v>69.09989329640791</v>
+        <v>69.3455615245893</v>
       </c>
       <c r="AK24">
-        <v>458.5120723172628</v>
+        <v>459.9928957913734</v>
       </c>
       <c r="AL24">
-        <v>87.39363905325443</v>
+        <v>87.40365076973637</v>
       </c>
       <c r="AM24">
-        <v>25.27516974169742</v>
+        <v>25.33384621974624</v>
       </c>
       <c r="AN24">
-        <v>32.36308133430938</v>
+        <v>32.48386224413566</v>
       </c>
       <c r="AO24">
-        <v>51.04342032892968</v>
+        <v>50.94222731885448</v>
       </c>
       <c r="AP24">
-        <v>1831.83290798451</v>
+        <v>1832.613016173703</v>
       </c>
       <c r="AQ24">
-        <v>228.5320419753087</v>
+        <v>228.7620235538954</v>
       </c>
       <c r="AR24">
-        <v>134.6961730060536</v>
+        <v>134.7064828407516</v>
       </c>
       <c r="AS24">
         <v>8.790017996400719</v>
@@ -3604,7 +3607,7 @@
         <v>2.607946802567986</v>
       </c>
       <c r="AU24">
-        <v>187.2110484848486</v>
+        <v>187.5279727940676</v>
       </c>
       <c r="AV24">
         <v>1</v>
@@ -3617,22 +3620,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>961.8720139066908</v>
+        <v>961.2834531502424</v>
       </c>
       <c r="C25">
-        <v>92.04650757575757</v>
+        <v>92.00885013525112</v>
       </c>
       <c r="D25">
-        <v>6742.376989425107</v>
+        <v>6740.79479215578</v>
       </c>
       <c r="E25">
-        <v>492.388457869577</v>
+        <v>491.484647553352</v>
       </c>
       <c r="F25">
-        <v>827.4780925154007</v>
+        <v>827.0467181008902</v>
       </c>
       <c r="G25">
-        <v>118.32339270904</v>
+        <v>118.3331940789474</v>
       </c>
       <c r="H25">
         <v>1.369760514840421</v>
@@ -3641,25 +3644,25 @@
         <v>230.4928383356719</v>
       </c>
       <c r="J25">
-        <v>82.37331214028336</v>
+        <v>82.4307103478867</v>
       </c>
       <c r="K25">
         <v>-1.235700942162778E-14</v>
       </c>
       <c r="L25">
-        <v>2917.626195382961</v>
+        <v>2915.583811443721</v>
       </c>
       <c r="M25">
-        <v>2755.595962926831</v>
+        <v>2744.517705634227</v>
       </c>
       <c r="N25">
-        <v>1084.586202808403</v>
+        <v>1084.456371298406</v>
       </c>
       <c r="O25">
-        <v>304.9162703024443</v>
+        <v>304.3778771658757</v>
       </c>
       <c r="P25">
-        <v>32.27975798869263</v>
+        <v>31.94989983048236</v>
       </c>
       <c r="Q25">
         <v>1.933270295595877</v>
@@ -3668,28 +3671,28 @@
         <v>10.95951879395962</v>
       </c>
       <c r="S25">
-        <v>50.13765196676725</v>
+        <v>50.09876536514867</v>
       </c>
       <c r="T25">
-        <v>133.1111790741765</v>
+        <v>132.3393709131905</v>
       </c>
       <c r="U25">
-        <v>93.92930347586636</v>
+        <v>93.85347368421053</v>
       </c>
       <c r="V25">
-        <v>294.5856996654202</v>
+        <v>293.859482023297</v>
       </c>
       <c r="W25">
-        <v>280.5774176468284</v>
+        <v>280.5228610763455</v>
       </c>
       <c r="Z25">
-        <v>3.07282262834242E-14</v>
+        <v>3.095328950463569E-14</v>
       </c>
       <c r="AA25">
-        <v>43.70482324975359</v>
+        <v>43.71964378801042</v>
       </c>
       <c r="AB25">
-        <v>73.2819932829555</v>
+        <v>73.43926779960694</v>
       </c>
       <c r="AC25">
         <v>-3.031606512162975E-15</v>
@@ -3707,43 +3710,43 @@
         <v>0.5513173933427098</v>
       </c>
       <c r="AH25">
-        <v>2074.150530314952</v>
+        <v>2071.737492795389</v>
       </c>
       <c r="AJ25">
-        <v>58.68854039693701</v>
+        <v>58.71738217763517</v>
       </c>
       <c r="AK25">
-        <v>439.837430523918</v>
+        <v>439.9264203855706</v>
       </c>
       <c r="AL25">
-        <v>98.23410853569644</v>
+        <v>98.24004366812228</v>
       </c>
       <c r="AM25">
-        <v>30.78268005879471</v>
+        <v>30.89711877757785</v>
       </c>
       <c r="AN25">
-        <v>18.77454162679426</v>
+        <v>18.70504788709334</v>
       </c>
       <c r="AO25">
-        <v>52.22162600539401</v>
+        <v>52.48758275382475</v>
       </c>
       <c r="AP25">
-        <v>2190.893646774453</v>
+        <v>2185.114691084215</v>
       </c>
       <c r="AQ25">
-        <v>240.3662410218267</v>
+        <v>240.5148792908336</v>
       </c>
       <c r="AR25">
         <v>43.51724447513812</v>
       </c>
       <c r="AS25">
-        <v>15.14837801096192</v>
+        <v>15.10559790819291</v>
       </c>
       <c r="AT25">
         <v>7.199172993492407</v>
       </c>
       <c r="AU25">
-        <v>154.1675230044175</v>
+        <v>154.4314161813904</v>
       </c>
       <c r="AV25">
         <v>1</v>
@@ -3874,88 +3877,88 @@
         </is>
       </c>
       <c r="B27">
-        <v>984.6613464315574</v>
+        <v>985.144291541897</v>
       </c>
       <c r="C27">
-        <v>96.85011402468436</v>
+        <v>97.33648772834249</v>
       </c>
       <c r="D27">
-        <v>6233.972346447952</v>
+        <v>6232.850597264043</v>
       </c>
       <c r="E27">
-        <v>336.657452133273</v>
+        <v>336.9498015250286</v>
       </c>
       <c r="F27">
-        <v>903.521941924335</v>
+        <v>903.6730527342636</v>
       </c>
       <c r="G27">
-        <v>66.40553221288515</v>
+        <v>66.42359538659821</v>
       </c>
       <c r="H27">
-        <v>0.7272419832720681</v>
+        <v>0.724898504922815</v>
       </c>
       <c r="I27">
-        <v>225.471025688377</v>
+        <v>225.6264645806688</v>
       </c>
       <c r="J27">
-        <v>61.91741285670048</v>
+        <v>62.03513850766026</v>
       </c>
       <c r="K27">
-        <v>7.644815836747533E-15</v>
+        <v>7.688239454955409E-15</v>
       </c>
       <c r="L27">
-        <v>2939.211647692496</v>
+        <v>2938.779573582998</v>
       </c>
       <c r="M27">
-        <v>2277.992139861865</v>
+        <v>2272.5925710672</v>
       </c>
       <c r="N27">
-        <v>881.0105422357938</v>
+        <v>882.1984578744764</v>
       </c>
       <c r="O27">
-        <v>141.8129115341545</v>
+        <v>142.0199807211495</v>
       </c>
       <c r="P27">
-        <v>53.5448124139083</v>
+        <v>53.7356090487239</v>
       </c>
       <c r="Q27">
-        <v>1.303768557289684</v>
+        <v>1.265490429438493</v>
       </c>
       <c r="R27">
         <v>0.391877288361256</v>
       </c>
       <c r="S27">
-        <v>61.34563792507818</v>
+        <v>61.41032654260432</v>
       </c>
       <c r="T27">
-        <v>226.837930250117</v>
+        <v>226.9160291360162</v>
       </c>
       <c r="U27">
-        <v>90.90912729221913</v>
+        <v>90.89088953163851</v>
       </c>
       <c r="V27">
-        <v>311.6924208862998</v>
+        <v>311.8241777747552</v>
       </c>
       <c r="W27">
-        <v>216.9638113400127</v>
+        <v>216.9661100524059</v>
       </c>
       <c r="Z27">
-        <v>3.985674411610244E-14</v>
+        <v>3.985802339362657E-14</v>
       </c>
       <c r="AA27">
-        <v>24.57464470602892</v>
+        <v>24.65260065111454</v>
       </c>
       <c r="AB27">
-        <v>42.94120987706486</v>
+        <v>42.86887031376708</v>
       </c>
       <c r="AC27">
-        <v>7.962875028518581E-16</v>
+        <v>7.797732714586282E-16</v>
       </c>
       <c r="AD27">
         <v>0.3071763771121409</v>
       </c>
       <c r="AE27">
-        <v>2.216957599118943</v>
+        <v>2.207743180090445</v>
       </c>
       <c r="AF27">
         <v>36.47156060606061</v>
@@ -3964,43 +3967,43 @@
         <v>0.1324166073286958</v>
       </c>
       <c r="AH27">
-        <v>2220.187604789995</v>
+        <v>2218.761419156039</v>
       </c>
       <c r="AJ27">
-        <v>54.12977607318107</v>
+        <v>54.23505548216644</v>
       </c>
       <c r="AK27">
-        <v>420.9186779911374</v>
+        <v>422.1737016286095</v>
       </c>
       <c r="AL27">
-        <v>94.53250177955429</v>
+        <v>94.55058266885379</v>
       </c>
       <c r="AM27">
-        <v>13.85927303244079</v>
+        <v>13.82911898700504</v>
       </c>
       <c r="AN27">
         <v>18.28115856201518</v>
       </c>
       <c r="AO27">
-        <v>54.13188763275099</v>
+        <v>54.11322350986235</v>
       </c>
       <c r="AP27">
-        <v>1632.630091790289</v>
+        <v>1630.560026160663</v>
       </c>
       <c r="AQ27">
-        <v>266.8468977311195</v>
+        <v>266.8474860579552</v>
       </c>
       <c r="AR27">
-        <v>132.4788648821375</v>
+        <v>132.6178726832292</v>
       </c>
       <c r="AS27">
-        <v>16.1118327588759</v>
+        <v>16.19726250826537</v>
       </c>
       <c r="AT27">
-        <v>3.049027973493434</v>
+        <v>3.025274558508285</v>
       </c>
       <c r="AU27">
-        <v>161.6110102802398</v>
+        <v>161.3584272812208</v>
       </c>
       <c r="AV27">
         <v>1</v>
@@ -4013,118 +4016,118 @@
         </is>
       </c>
       <c r="B28">
-        <v>501.3242046659597</v>
+        <v>508.2120899562148</v>
       </c>
       <c r="C28">
-        <v>46.31299189401768</v>
+        <v>48.93300974989403</v>
       </c>
       <c r="D28">
-        <v>8260.657360562143</v>
+        <v>8363.702772926119</v>
       </c>
       <c r="E28">
-        <v>159.4887790697674</v>
+        <v>159.8499564033482</v>
       </c>
       <c r="F28">
-        <v>466.1273370754448</v>
+        <v>466.6126730317984</v>
       </c>
       <c r="G28">
-        <v>10.71684719963952</v>
+        <v>10.8744979707076</v>
       </c>
       <c r="H28">
-        <v>10.99809000707175</v>
+        <v>13.67206952965235</v>
       </c>
       <c r="I28">
-        <v>157.9050703971119</v>
+        <v>159.0620146477527</v>
       </c>
       <c r="J28">
-        <v>29.30850253023861</v>
+        <v>29.56023592715232</v>
       </c>
       <c r="K28">
-        <v>-2.516802959798617E-15</v>
+        <v>-2.768892632169509E-15</v>
       </c>
       <c r="L28">
-        <v>5015.987195200342</v>
+        <v>5035.943636151573</v>
       </c>
       <c r="M28">
-        <v>1732.004210836278</v>
+        <v>1727.843276322929</v>
       </c>
       <c r="N28">
-        <v>1431.829684960481</v>
+        <v>1456.745573856517</v>
       </c>
       <c r="O28">
-        <v>119.246338028169</v>
+        <v>118.0721365712342</v>
       </c>
       <c r="P28">
-        <v>25.56626248708233</v>
+        <v>26.32735507025597</v>
       </c>
       <c r="Q28">
         <v>0.9081785102739727</v>
       </c>
       <c r="S28">
-        <v>1.056811757628068</v>
+        <v>1.081255989045626</v>
       </c>
       <c r="T28">
-        <v>13.60980841330315</v>
+        <v>13.54209793491865</v>
       </c>
       <c r="U28">
-        <v>99.55552768684092</v>
+        <v>102.245176730486</v>
       </c>
       <c r="V28">
-        <v>182.2088268389248</v>
+        <v>182.7395931026956</v>
       </c>
       <c r="W28">
-        <v>130.0576689189189</v>
+        <v>129.7322662675447</v>
       </c>
       <c r="Z28">
-        <v>1.271603733773182E-14</v>
+        <v>1.391861810460722E-14</v>
       </c>
       <c r="AA28">
-        <v>4.316036513545347</v>
+        <v>4.338099667898861</v>
       </c>
       <c r="AB28">
-        <v>4.647012211668929</v>
+        <v>4.581612842847452</v>
       </c>
       <c r="AC28">
-        <v>7.707582218414647E-17</v>
+        <v>7.821591862512283E-17</v>
       </c>
       <c r="AD28">
         <v>0.0008327328758771298</v>
       </c>
       <c r="AF28">
-        <v>17.3006440061268</v>
+        <v>20.92921848260125</v>
       </c>
       <c r="AG28">
         <v>1.699354707792208</v>
       </c>
       <c r="AH28">
-        <v>3243.038623721881</v>
+        <v>3238.079849067873</v>
       </c>
       <c r="AJ28">
-        <v>74.95777747625507</v>
+        <v>76.75247382675195</v>
       </c>
       <c r="AK28">
-        <v>1025.54998268262</v>
+        <v>1044.685190690236</v>
       </c>
       <c r="AL28">
-        <v>118.6586219031531</v>
+        <v>118.6014356938446</v>
       </c>
       <c r="AM28">
-        <v>60.42723063954682</v>
+        <v>57.43492291880781</v>
       </c>
       <c r="AN28">
-        <v>48.12835278154682</v>
+        <v>48.42029738330744</v>
       </c>
       <c r="AO28">
-        <v>138.5282464581668</v>
+        <v>143.5156356864252</v>
       </c>
       <c r="AP28">
-        <v>1179.840509013786</v>
+        <v>1163.641040713106</v>
       </c>
       <c r="AQ28">
-        <v>80.44934871794872</v>
+        <v>79.65346760710509</v>
       </c>
       <c r="AR28">
-        <v>15.52628247834777</v>
+        <v>15.22918199289869</v>
       </c>
       <c r="AS28">
         <v>6.807825722664433</v>
@@ -4133,7 +4136,7 @@
         <v>3.031521572910978</v>
       </c>
       <c r="AU28">
-        <v>350.8799200685126</v>
+        <v>349.861917922377</v>
       </c>
       <c r="AV28">
         <v>1</v>

--- a/base_datas/mediana_uf_detalhamento.xlsx
+++ b/base_datas/mediana_uf_detalhamento.xlsx
@@ -603,22 +603,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>283.9583954907779</v>
+        <v>285.5637434237151</v>
       </c>
       <c r="C2">
-        <v>39.80510115453872</v>
+        <v>39.35472068928102</v>
       </c>
       <c r="D2">
-        <v>4759.685129558606</v>
+        <v>4739.746970517682</v>
       </c>
       <c r="E2">
-        <v>145.0513119290826</v>
+        <v>147.8351081595781</v>
       </c>
       <c r="F2">
-        <v>279.239839568117</v>
+        <v>285.5560643464185</v>
       </c>
       <c r="G2">
-        <v>11.10129639374646</v>
+        <v>10.94486028033211</v>
       </c>
       <c r="H2">
         <v>34.49796639466256</v>
@@ -627,49 +627,49 @@
         <v>146.1711518736456</v>
       </c>
       <c r="J2">
-        <v>39.80510115453872</v>
+        <v>39.35472068928102</v>
       </c>
       <c r="K2">
         <v>-9.57655712571925E-15</v>
       </c>
       <c r="L2">
-        <v>2739.744731038375</v>
+        <v>2573.469552814637</v>
       </c>
       <c r="M2">
-        <v>770.5855750411912</v>
+        <v>770.8154368180764</v>
       </c>
       <c r="N2">
-        <v>1313.985043231271</v>
+        <v>1368.07551264525</v>
       </c>
       <c r="O2">
-        <v>121.9991253113552</v>
+        <v>124.4543191006258</v>
       </c>
       <c r="P2">
         <v>5.567369628518485</v>
       </c>
       <c r="S2">
-        <v>0.3205017313855276</v>
+        <v>0.3016065529856479</v>
       </c>
       <c r="T2">
-        <v>8.254262402294792</v>
+        <v>9.335962311209643</v>
       </c>
       <c r="U2">
-        <v>20.20036474962382</v>
+        <v>15.10645675752819</v>
       </c>
       <c r="V2">
-        <v>90.02096352252764</v>
+        <v>90.21163015555872</v>
       </c>
       <c r="W2">
-        <v>130.1075390437837</v>
+        <v>136.0283599374022</v>
       </c>
       <c r="Z2">
-        <v>2.941785340737871E-14</v>
+        <v>3.226141660715943E-14</v>
       </c>
       <c r="AA2">
-        <v>4.732662670168948</v>
+        <v>4.553415579119087</v>
       </c>
       <c r="AB2">
-        <v>8.802885619871919</v>
+        <v>8.201769280205655</v>
       </c>
       <c r="AC2">
         <v>-1.408619160560911E-16</v>
@@ -678,43 +678,43 @@
         <v>34.49796639466256</v>
       </c>
       <c r="AH2">
-        <v>1420.316144546597</v>
+        <v>1404.303908179653</v>
       </c>
       <c r="AJ2">
-        <v>24.43361282342864</v>
+        <v>24.12032175887468</v>
       </c>
       <c r="AK2">
-        <v>697.5568566191579</v>
+        <v>686.7130289203085</v>
       </c>
       <c r="AL2">
-        <v>138.6253725730148</v>
+        <v>141.2635355567593</v>
       </c>
       <c r="AM2">
-        <v>210.4724438042965</v>
+        <v>219.4668180762981</v>
       </c>
       <c r="AN2">
-        <v>32.21932287438311</v>
+        <v>31.03121001611841</v>
       </c>
       <c r="AO2">
-        <v>207.7041951684839</v>
+        <v>200.9404325653403</v>
       </c>
       <c r="AP2">
-        <v>647.8717564960864</v>
+        <v>656.8697915402968</v>
       </c>
       <c r="AQ2">
-        <v>43.65787379404382</v>
+        <v>42.66190784081595</v>
       </c>
       <c r="AR2">
-        <v>2.489077104813607</v>
+        <v>2.476773082942097</v>
       </c>
       <c r="AS2">
-        <v>6.021043940264216</v>
+        <v>6.033916857977701</v>
       </c>
       <c r="AT2">
         <v>0.04486931973408614</v>
       </c>
       <c r="AU2">
-        <v>40.44255735079063</v>
+        <v>46.12002249357328</v>
       </c>
       <c r="AV2">
         <v>1</v>
@@ -730,10 +730,10 @@
         <v>341.2111347016007</v>
       </c>
       <c r="C3">
-        <v>259.3472432054568</v>
+        <v>261.40361102601</v>
       </c>
       <c r="D3">
-        <v>8018.469716132185</v>
+        <v>7982.322781391018</v>
       </c>
       <c r="E3">
         <v>231.9742618959338</v>
@@ -742,16 +742,16 @@
         <v>327.6135269189371</v>
       </c>
       <c r="G3">
-        <v>9.009045629556811</v>
+        <v>8.935345509813867</v>
       </c>
       <c r="H3">
-        <v>82.99977930805608</v>
+        <v>85.54520903574972</v>
       </c>
       <c r="I3">
-        <v>198.5066795515491</v>
+        <v>199.3934640795206</v>
       </c>
       <c r="J3">
-        <v>102.6400065879698</v>
+        <v>102.5030161090458</v>
       </c>
       <c r="K3">
         <v>1.159420708809301E-14</v>
@@ -760,37 +760,37 @@
         <v>5257.196750971281</v>
       </c>
       <c r="M3">
-        <v>1041.368728120803</v>
+        <v>1032.827548729685</v>
       </c>
       <c r="N3">
         <v>1566.593200656242</v>
       </c>
       <c r="O3">
-        <v>180.8912265697908</v>
+        <v>177.721577095833</v>
       </c>
       <c r="P3">
-        <v>40.19938480128923</v>
+        <v>41.60439422008151</v>
       </c>
       <c r="S3">
-        <v>11.13753632755408</v>
+        <v>11.29426860223071</v>
       </c>
       <c r="T3">
-        <v>6.021365230217262</v>
+        <v>6.739001045162713</v>
       </c>
       <c r="U3">
         <v>5.831349378575656</v>
       </c>
       <c r="V3">
-        <v>100.8135594191041</v>
+        <v>100.706403956017</v>
       </c>
       <c r="W3">
         <v>160.0005603313581</v>
       </c>
       <c r="Z3">
-        <v>2.385078362492537E-14</v>
+        <v>2.424441846872607E-14</v>
       </c>
       <c r="AA3">
-        <v>7.025822281167109</v>
+        <v>7.036268611015609</v>
       </c>
       <c r="AB3">
         <v>3.020586624262398</v>
@@ -802,13 +802,13 @@
         <v>69.36389114743217</v>
       </c>
       <c r="AF3">
-        <v>108.3593809423199</v>
+        <v>105.2351290063619</v>
       </c>
       <c r="AG3">
         <v>0.1124137542488116</v>
       </c>
       <c r="AH3">
-        <v>2588.354052280334</v>
+        <v>2564.900011632566</v>
       </c>
       <c r="AJ3">
         <v>50.31833502661729</v>
@@ -826,22 +826,22 @@
         <v>35.00160496444995</v>
       </c>
       <c r="AO3">
-        <v>18.87146364271179</v>
+        <v>19.46276557439087</v>
       </c>
       <c r="AP3">
-        <v>833.0761109020865</v>
+        <v>824.583835280682</v>
       </c>
       <c r="AQ3">
         <v>56.8624218172268</v>
       </c>
       <c r="AR3">
-        <v>42.49126534466478</v>
+        <v>45.22218219122466</v>
       </c>
       <c r="AS3">
-        <v>5.532847388817125</v>
+        <v>5.527442203458568</v>
       </c>
       <c r="AT3">
-        <v>4.409734222159909</v>
+        <v>4.407810921513979</v>
       </c>
       <c r="AU3">
         <v>61.15165496520426</v>
@@ -981,22 +981,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>413.4902098740756</v>
+        <v>398.1741506071476</v>
       </c>
       <c r="C5">
-        <v>68.51538084924498</v>
+        <v>43.74565464426878</v>
       </c>
       <c r="D5">
-        <v>6538.38245446515</v>
+        <v>6447.36629671723</v>
       </c>
       <c r="E5">
-        <v>209.6835760039729</v>
+        <v>188.0818522931034</v>
       </c>
       <c r="F5">
-        <v>374.0262391340003</v>
+        <v>365.2811543880227</v>
       </c>
       <c r="G5">
-        <v>12.60067356468474</v>
+        <v>12.97267417430036</v>
       </c>
       <c r="H5">
         <v>9.114944438413008</v>
@@ -1005,49 +1005,49 @@
         <v>94.22497703493447</v>
       </c>
       <c r="J5">
-        <v>40.00470122262512</v>
+        <v>36.26374780098146</v>
       </c>
       <c r="K5">
         <v>-1.913493609694627E-14</v>
       </c>
       <c r="L5">
-        <v>3630.728121019108</v>
+        <v>3562.132600660145</v>
       </c>
       <c r="M5">
-        <v>1220.800751640906</v>
+        <v>1144.613048808293</v>
       </c>
       <c r="N5">
-        <v>1657.196671974522</v>
+        <v>1600.257269733586</v>
       </c>
       <c r="O5">
-        <v>165.9859248676359</v>
+        <v>159.3951861253547</v>
       </c>
       <c r="P5">
         <v>19.3318941806601</v>
       </c>
       <c r="S5">
-        <v>0.0361522857166593</v>
+        <v>0.01807614285890483</v>
       </c>
       <c r="T5">
         <v>1.522509883925305</v>
       </c>
       <c r="U5">
-        <v>1.433229457110054</v>
+        <v>1.6772961649263</v>
       </c>
       <c r="V5">
-        <v>206.7065011580776</v>
+        <v>218.4175506253098</v>
       </c>
       <c r="W5">
-        <v>160.9533127470356</v>
+        <v>140.7454415356044</v>
       </c>
       <c r="Z5">
-        <v>-3.2409610753601E-14</v>
+        <v>-3.188324067919991E-14</v>
       </c>
       <c r="AA5">
-        <v>10.4491728470465</v>
+        <v>9.141095332209222</v>
       </c>
       <c r="AB5">
-        <v>9.365043096257695</v>
+        <v>12.97267417430036</v>
       </c>
       <c r="AC5">
         <v>2.616779913327972E-16</v>
@@ -1059,40 +1059,40 @@
         <v>12.04646692999412</v>
       </c>
       <c r="AH5">
-        <v>1429.207058482918</v>
+        <v>1394.705685725197</v>
       </c>
       <c r="AJ5">
-        <v>42.11441806601042</v>
+        <v>40.47899073954766</v>
       </c>
       <c r="AK5">
-        <v>1112.848383460228</v>
+        <v>1103.86844197715</v>
       </c>
       <c r="AL5">
-        <v>125.2594172616548</v>
+        <v>122.1390119905112</v>
       </c>
       <c r="AM5">
-        <v>72.64713520474027</v>
+        <v>56.39780457949308</v>
       </c>
       <c r="AN5">
-        <v>34.37591445852534</v>
+        <v>31.18591867135621</v>
       </c>
       <c r="AO5">
-        <v>452.2476249890937</v>
+        <v>383.611979231212</v>
       </c>
       <c r="AP5">
-        <v>648.4116849890066</v>
+        <v>611.2221751803496</v>
       </c>
       <c r="AQ5">
-        <v>12.78723930509401</v>
+        <v>14.61242778447267</v>
       </c>
       <c r="AR5">
-        <v>64.83804046233173</v>
+        <v>62.60868736080178</v>
       </c>
       <c r="AS5">
         <v>35.22086107921929</v>
       </c>
       <c r="AU5">
-        <v>205.6153018129811</v>
+        <v>196.7958367503846</v>
       </c>
       <c r="AV5">
         <v>1</v>
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>350.8147021768041</v>
+        <v>352.481087679455</v>
       </c>
       <c r="C6">
-        <v>32.55126664973344</v>
+        <v>33.12601676806608</v>
       </c>
       <c r="D6">
-        <v>5977.657846673373</v>
+        <v>5996.077022990088</v>
       </c>
       <c r="E6">
-        <v>103.625537640387</v>
+        <v>103.4738451701751</v>
       </c>
       <c r="F6">
-        <v>328.500579683218</v>
+        <v>329.9292869345614</v>
       </c>
       <c r="G6">
-        <v>17.51428034651915</v>
+        <v>17.61150656509352</v>
       </c>
       <c r="H6">
         <v>5.773593827775013</v>
@@ -1129,55 +1129,55 @@
         <v>209.9288514485036</v>
       </c>
       <c r="J6">
-        <v>28.71299786465505</v>
+        <v>29.61181043300375</v>
       </c>
       <c r="K6">
         <v>9.273740571928618E-15</v>
       </c>
       <c r="L6">
-        <v>4183.808065748052</v>
+        <v>4200.450257505004</v>
       </c>
       <c r="M6">
-        <v>638.8528061164935</v>
+        <v>641.1364493741479</v>
       </c>
       <c r="N6">
-        <v>1052.935800706844</v>
+        <v>1049.764736703452</v>
       </c>
       <c r="O6">
-        <v>72.28900907220351</v>
+        <v>71.87268982409263</v>
       </c>
       <c r="P6">
-        <v>11.2406980760256</v>
+        <v>11.42888621966115</v>
       </c>
       <c r="Q6">
         <v>2.890179627836936</v>
       </c>
       <c r="S6">
-        <v>7.526826259557396</v>
+        <v>7.769335078533388</v>
       </c>
       <c r="T6">
-        <v>12.0812979966611</v>
+        <v>12.21911559193452</v>
       </c>
       <c r="U6">
-        <v>7.419998755367478</v>
+        <v>7.624317419473417</v>
       </c>
       <c r="V6">
-        <v>109.5133235760338</v>
+        <v>109.8786918025557</v>
       </c>
       <c r="W6">
-        <v>166.8159015987111</v>
+        <v>167.0460833271223</v>
       </c>
       <c r="Z6">
-        <v>1.996489827249782E-14</v>
+        <v>1.902832981806715E-14</v>
       </c>
       <c r="AA6">
-        <v>15.17767611440873</v>
+        <v>15.33008449913827</v>
       </c>
       <c r="AB6">
-        <v>1.883380391419592</v>
+        <v>1.873304118367732</v>
       </c>
       <c r="AC6">
-        <v>-2.021347908133619E-16</v>
+        <v>-2.058199412660586E-16</v>
       </c>
       <c r="AD6">
         <v>0.1351699846782949</v>
@@ -1189,40 +1189,40 @@
         <v>0.1804582074521651</v>
       </c>
       <c r="AH6">
-        <v>2250.765603366898</v>
+        <v>2288.450384451317</v>
       </c>
       <c r="AJ6">
-        <v>45.79033585326558</v>
+        <v>46.09572236358496</v>
       </c>
       <c r="AK6">
-        <v>650.8421110089175</v>
+        <v>649.3149512023984</v>
       </c>
       <c r="AL6">
-        <v>148.861337306761</v>
+        <v>149.1982874328892</v>
       </c>
       <c r="AM6">
-        <v>808.6973780015492</v>
+        <v>806.6851672097411</v>
       </c>
       <c r="AN6">
         <v>32.10897424745097</v>
       </c>
       <c r="AO6">
-        <v>20.71018340332767</v>
+        <v>20.96198278256061</v>
       </c>
       <c r="AP6">
-        <v>493.7454685494223</v>
+        <v>499.8405740612762</v>
       </c>
       <c r="AQ6">
-        <v>40.43931626826672</v>
+        <v>40.79824387974647</v>
       </c>
       <c r="AR6">
-        <v>23.96999779371208</v>
+        <v>23.97479994985103</v>
       </c>
       <c r="AS6">
-        <v>9.211068043877695</v>
+        <v>9.211187063005351</v>
       </c>
       <c r="AT6">
-        <v>1.196950380553695</v>
+        <v>1.117301568007779</v>
       </c>
       <c r="AU6">
         <v>34.80163155365587</v>
@@ -1480,76 +1480,76 @@
         </is>
       </c>
       <c r="B9">
-        <v>545.7378921718523</v>
+        <v>549.2981223470333</v>
       </c>
       <c r="C9">
-        <v>132.6241103282866</v>
+        <v>136.8373080161188</v>
       </c>
       <c r="D9">
-        <v>6532.525897978622</v>
+        <v>6517.432708749699</v>
       </c>
       <c r="E9">
-        <v>349.4722130529491</v>
+        <v>365.6114772037478</v>
       </c>
       <c r="F9">
-        <v>474.6869633972992</v>
+        <v>483.9849966648892</v>
       </c>
       <c r="G9">
-        <v>53.01504975124379</v>
+        <v>53.08038858006523</v>
       </c>
       <c r="H9">
         <v>0.5835266396125148</v>
       </c>
       <c r="I9">
-        <v>138.5467381005542</v>
+        <v>138.1220880516457</v>
       </c>
       <c r="J9">
-        <v>89.8292738740452</v>
+        <v>91.49776464038524</v>
       </c>
       <c r="K9">
-        <v>8.430700958862792E-15</v>
+        <v>8.433448408210288E-15</v>
       </c>
       <c r="L9">
-        <v>3279.145877178284</v>
+        <v>3275.403100052637</v>
       </c>
       <c r="M9">
-        <v>2089.162812077871</v>
+        <v>2072.912872383251</v>
       </c>
       <c r="N9">
-        <v>1113.784550225981</v>
+        <v>1113.590140596729</v>
       </c>
       <c r="O9">
-        <v>206.8651069696682</v>
+        <v>205.7835205246351</v>
       </c>
       <c r="P9">
-        <v>94.2962349609916</v>
+        <v>99.42889528394028</v>
       </c>
       <c r="Q9">
         <v>0.769951680159711</v>
       </c>
       <c r="S9">
-        <v>35.6182305816803</v>
+        <v>35.40801053445175</v>
       </c>
       <c r="T9">
-        <v>58.23257376523413</v>
+        <v>58.71250559275737</v>
       </c>
       <c r="U9">
-        <v>44.80726372705811</v>
+        <v>45.70847705516775</v>
       </c>
       <c r="V9">
-        <v>230.4731929936596</v>
+        <v>231.5306820700607</v>
       </c>
       <c r="W9">
-        <v>156.8528275566048</v>
+        <v>156.8423622824711</v>
       </c>
       <c r="Z9">
-        <v>-2.05935471124951E-14</v>
+        <v>-2.108196179294709E-14</v>
       </c>
       <c r="AA9">
-        <v>17.35673148568832</v>
+        <v>17.3478338026256</v>
       </c>
       <c r="AB9">
-        <v>35.37594785442694</v>
+        <v>35.45732977171394</v>
       </c>
       <c r="AC9">
         <v>6.629936592600439E-17</v>
@@ -1567,43 +1567,43 @@
         <v>0.7783757766095443</v>
       </c>
       <c r="AH9">
-        <v>1932.526450400248</v>
+        <v>1931.699866238566</v>
       </c>
       <c r="AJ9">
-        <v>190.7531598062954</v>
+        <v>189.4986884685337</v>
       </c>
       <c r="AK9">
-        <v>540.7165715004402</v>
+        <v>540.0383913644503</v>
       </c>
       <c r="AL9">
-        <v>105.615641492929</v>
+        <v>105.5136678439629</v>
       </c>
       <c r="AM9">
-        <v>122.9130624559105</v>
+        <v>119.0603606897511</v>
       </c>
       <c r="AN9">
-        <v>21.23644201030928</v>
+        <v>21.26214276889795</v>
       </c>
       <c r="AO9">
-        <v>22.88135181265783</v>
+        <v>22.7865684012579</v>
       </c>
       <c r="AP9">
-        <v>1485.060486709982</v>
+        <v>1483.6711940687</v>
       </c>
       <c r="AQ9">
-        <v>154.4604296223639</v>
+        <v>154.4518904631188</v>
       </c>
       <c r="AR9">
-        <v>7.486446280991736</v>
+        <v>7.554550292046143</v>
       </c>
       <c r="AS9">
-        <v>34.15310754414983</v>
+        <v>33.94106557377049</v>
       </c>
       <c r="AT9">
-        <v>27.03334577114428</v>
+        <v>26.89676916436718</v>
       </c>
       <c r="AU9">
-        <v>221.7188168585555</v>
+        <v>220.2538001237685</v>
       </c>
       <c r="AV9">
         <v>1</v>
@@ -1619,10 +1619,10 @@
         <v>842.1912774017301</v>
       </c>
       <c r="C10">
-        <v>289.7960718981939</v>
+        <v>290.7962556545473</v>
       </c>
       <c r="D10">
-        <v>7779.616688941662</v>
+        <v>7824.881479716631</v>
       </c>
       <c r="E10">
         <v>348.589878111765</v>
@@ -1631,13 +1631,13 @@
         <v>802.0819527194764</v>
       </c>
       <c r="G10">
-        <v>40.13066415239069</v>
+        <v>40.07986222479403</v>
       </c>
       <c r="H10">
         <v>6.581133333333334</v>
       </c>
       <c r="I10">
-        <v>300.7929783136822</v>
+        <v>305.5469827134625</v>
       </c>
       <c r="J10">
         <v>56.95789947937525</v>
@@ -1649,7 +1649,7 @@
         <v>4154.19768983191</v>
       </c>
       <c r="M10">
-        <v>2482.627966682026</v>
+        <v>2491.556394500443</v>
       </c>
       <c r="N10">
         <v>838.8127846930881</v>
@@ -1670,7 +1670,7 @@
         <v>53.72012190240643</v>
       </c>
       <c r="T10">
-        <v>67.41809940752637</v>
+        <v>67.26801759480942</v>
       </c>
       <c r="U10">
         <v>149.0841759486314</v>
@@ -1679,13 +1679,13 @@
         <v>273.7698316520127</v>
       </c>
       <c r="W10">
-        <v>215.2670824283694</v>
+        <v>215.4485881220159</v>
       </c>
       <c r="Z10">
         <v>-1.674077104212465E-14</v>
       </c>
       <c r="AA10">
-        <v>20.96008654553387</v>
+        <v>20.85251623376623</v>
       </c>
       <c r="AB10">
         <v>14.39772070242397</v>
@@ -1706,7 +1706,7 @@
         <v>1.470845643041063</v>
       </c>
       <c r="AH10">
-        <v>2677.950561169912</v>
+        <v>2741.548801693074</v>
       </c>
       <c r="AJ10">
         <v>74.38103382072444</v>
@@ -1715,19 +1715,19 @@
         <v>541.6088506558663</v>
       </c>
       <c r="AL10">
-        <v>86.48370835929539</v>
+        <v>86.73649525355638</v>
       </c>
       <c r="AM10">
-        <v>36.55220325189012</v>
+        <v>36.72765145410592</v>
       </c>
       <c r="AN10">
-        <v>34.2899358226371</v>
+        <v>34.36837026539551</v>
       </c>
       <c r="AO10">
-        <v>268.4811393475919</v>
+        <v>270.5849748933834</v>
       </c>
       <c r="AP10">
-        <v>1866.184977532371</v>
+        <v>1876.79559223935</v>
       </c>
       <c r="AQ10">
         <v>167.1408913344304</v>
@@ -1736,13 +1736,13 @@
         <v>52.32232836905195</v>
       </c>
       <c r="AS10">
-        <v>23.12881464824928</v>
+        <v>22.95983163076797</v>
       </c>
       <c r="AT10">
         <v>7.992159680439119</v>
       </c>
       <c r="AU10">
-        <v>187.9808272846278</v>
+        <v>187.1305839314047</v>
       </c>
       <c r="AV10">
         <v>1</v>
@@ -1755,22 +1755,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>271.3840453074433</v>
+        <v>271.5784696484473</v>
       </c>
       <c r="C11">
         <v>48.3931805909126</v>
       </c>
       <c r="D11">
-        <v>6380.392780884303</v>
+        <v>6388.849777029231</v>
       </c>
       <c r="E11">
-        <v>92.96760541191735</v>
+        <v>93.71361697548815</v>
       </c>
       <c r="F11">
-        <v>253.4598772169168</v>
+        <v>253.5670255373588</v>
       </c>
       <c r="G11">
-        <v>4.678517422434368</v>
+        <v>4.587148526031998</v>
       </c>
       <c r="H11">
         <v>13.64586692122755</v>
@@ -1785,16 +1785,16 @@
         <v>1.073216045359242E-14</v>
       </c>
       <c r="L11">
-        <v>4648.701299174356</v>
+        <v>4649.805538169048</v>
       </c>
       <c r="M11">
-        <v>576.3831793276677</v>
+        <v>578.9442438812068</v>
       </c>
       <c r="N11">
-        <v>1039.309296363591</v>
+        <v>1036.59869045596</v>
       </c>
       <c r="O11">
-        <v>72.99974335281181</v>
+        <v>73.22981169188577</v>
       </c>
       <c r="P11">
         <v>9.079408226479135</v>
@@ -1803,28 +1803,28 @@
         <v>0.05101405951883867</v>
       </c>
       <c r="S11">
-        <v>2.932098995410381</v>
+        <v>2.963731019523886</v>
       </c>
       <c r="T11">
-        <v>1.161711366856404</v>
+        <v>1.151686856956018</v>
       </c>
       <c r="U11">
-        <v>4.840383921172424</v>
+        <v>4.887150980272834</v>
       </c>
       <c r="V11">
-        <v>82.05098882110903</v>
+        <v>82.19318062894372</v>
       </c>
       <c r="W11">
-        <v>142.0566528246388</v>
+        <v>141.7180301467265</v>
       </c>
       <c r="Z11">
-        <v>4.667283975587595E-16</v>
+        <v>-1.184478875777693E-15</v>
       </c>
       <c r="AA11">
         <v>3.283239521752231</v>
       </c>
       <c r="AB11">
-        <v>1.949293780337517</v>
+        <v>2.045687992376633</v>
       </c>
       <c r="AC11">
         <v>1.022648555459479E-16</v>
@@ -1842,31 +1842,31 @@
         <v>0.8486997964094021</v>
       </c>
       <c r="AH11">
-        <v>1917.480914938862</v>
+        <v>1922.770145910326</v>
       </c>
       <c r="AJ11">
-        <v>35.57198992090712</v>
+        <v>35.64493605789381</v>
       </c>
       <c r="AK11">
-        <v>790.3856025809274</v>
+        <v>789.1633843062193</v>
       </c>
       <c r="AL11">
-        <v>177.0625143272992</v>
+        <v>177.0163794749948</v>
       </c>
       <c r="AM11">
-        <v>1463.404233380704</v>
+        <v>1463.094656275588</v>
       </c>
       <c r="AN11">
-        <v>35.10222986111111</v>
+        <v>35.15311252946985</v>
       </c>
       <c r="AO11">
-        <v>47.50966262135946</v>
+        <v>49.25667809835592</v>
       </c>
       <c r="AP11">
-        <v>474.1814182334641</v>
+        <v>477.7072669588323</v>
       </c>
       <c r="AQ11">
-        <v>34.86353848617487</v>
+        <v>35.03344355979931</v>
       </c>
       <c r="AR11">
         <v>21.19330543933054</v>
@@ -1878,7 +1878,7 @@
         <v>0.2568273264275319</v>
       </c>
       <c r="AU11">
-        <v>15.98991570002732</v>
+        <v>15.8198728761286</v>
       </c>
       <c r="AV11">
         <v>1</v>
@@ -1894,19 +1894,19 @@
         <v>471.1061763022324</v>
       </c>
       <c r="C12">
-        <v>95.94523588817876</v>
+        <v>95.586116368029</v>
       </c>
       <c r="D12">
         <v>6336.80887034861</v>
       </c>
       <c r="E12">
-        <v>276.8376930099113</v>
+        <v>277.0701812249337</v>
       </c>
       <c r="F12">
         <v>429.8226617820846</v>
       </c>
       <c r="G12">
-        <v>33.31708564153057</v>
+        <v>33.31756974581526</v>
       </c>
       <c r="H12">
         <v>0.7983256145350909</v>
@@ -1924,16 +1924,16 @@
         <v>3773.589144505417</v>
       </c>
       <c r="M12">
-        <v>1555.481336717929</v>
+        <v>1554.221706341649</v>
       </c>
       <c r="N12">
-        <v>800.2877821363913</v>
+        <v>800.1033541142584</v>
       </c>
       <c r="O12">
-        <v>201.9386756019991</v>
+        <v>202.4792998239781</v>
       </c>
       <c r="P12">
-        <v>10.16855529318787</v>
+        <v>10.19370380078637</v>
       </c>
       <c r="Q12">
         <v>0.8076131687242798</v>
@@ -1945,25 +1945,25 @@
         <v>20.36292619089226</v>
       </c>
       <c r="T12">
-        <v>43.37962820891119</v>
+        <v>43.49920906679527</v>
       </c>
       <c r="U12">
-        <v>46.65965869660025</v>
+        <v>46.68175382841687</v>
       </c>
       <c r="V12">
-        <v>147.3945575447854</v>
+        <v>147.6024089443141</v>
       </c>
       <c r="W12">
-        <v>146.0594726017296</v>
+        <v>146.0333997785161</v>
       </c>
       <c r="Z12">
-        <v>1.171887676937133E-14</v>
+        <v>1.141917484903138E-14</v>
       </c>
       <c r="AA12">
         <v>11.95248037116346</v>
       </c>
       <c r="AB12">
-        <v>18.73349590373784</v>
+        <v>18.93649279161206</v>
       </c>
       <c r="AC12">
         <v>7.79019294734521E-17</v>
@@ -1984,40 +1984,40 @@
         <v>2641.514109957709</v>
       </c>
       <c r="AJ12">
-        <v>71.21413351100733</v>
+        <v>71.27843756283933</v>
       </c>
       <c r="AK12">
-        <v>613.7223436001248</v>
+        <v>613.3106758448059</v>
       </c>
       <c r="AL12">
-        <v>76.81353945154052</v>
+        <v>76.78203424956369</v>
       </c>
       <c r="AM12">
-        <v>31.96393883651415</v>
+        <v>31.73203786291205</v>
       </c>
       <c r="AN12">
-        <v>29.47392641874218</v>
+        <v>29.10599437489864</v>
       </c>
       <c r="AO12">
         <v>22.00650663008598</v>
       </c>
       <c r="AP12">
-        <v>930.3908059626074</v>
+        <v>930.1663274823857</v>
       </c>
       <c r="AQ12">
-        <v>186.8084611137948</v>
+        <v>186.8289259049835</v>
       </c>
       <c r="AR12">
-        <v>225.5150443932917</v>
+        <v>225.8552412701862</v>
       </c>
       <c r="AS12">
-        <v>10.64599470085754</v>
+        <v>10.68756679729248</v>
       </c>
       <c r="AT12">
         <v>1.939815386163185</v>
       </c>
       <c r="AU12">
-        <v>111.3117358384742</v>
+        <v>111.1532541987461</v>
       </c>
       <c r="AV12">
         <v>1</v>
@@ -2093,7 +2093,7 @@
         <v>404.1089236972443</v>
       </c>
       <c r="W13">
-        <v>343.5872743167828</v>
+        <v>344.9623400104059</v>
       </c>
       <c r="Z13">
         <v>5.109287186328324E-14</v>
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>1217.008394696597</v>
+        <v>1210.444867930172</v>
       </c>
       <c r="C14">
-        <v>307.8882896474652</v>
+        <v>307.6854554901282</v>
       </c>
       <c r="D14">
-        <v>8210.499215340811</v>
+        <v>8285.902551361933</v>
       </c>
       <c r="E14">
-        <v>469.5137284460254</v>
+        <v>474.1476874052526</v>
       </c>
       <c r="F14">
-        <v>1104.891272781036</v>
+        <v>1083.325346638378</v>
       </c>
       <c r="G14">
         <v>70.1917068912965</v>
@@ -2190,16 +2190,16 @@
         <v>235.2435950028662</v>
       </c>
       <c r="J14">
-        <v>92.71886059541902</v>
+        <v>91.79375824693686</v>
       </c>
       <c r="K14">
-        <v>7.106812019524112E-15</v>
+        <v>5.519581195315573E-15</v>
       </c>
       <c r="L14">
-        <v>3201.520331169863</v>
+        <v>3244.303130229067</v>
       </c>
       <c r="M14">
-        <v>3698.514659423688</v>
+        <v>3763.89708986257</v>
       </c>
       <c r="N14">
         <v>1227.665646941396</v>
@@ -2208,31 +2208,31 @@
         <v>274.5538544478901</v>
       </c>
       <c r="P14">
-        <v>93.29317893164614</v>
+        <v>89.48052764045616</v>
       </c>
       <c r="Q14">
         <v>1.248993123548431</v>
       </c>
       <c r="S14">
-        <v>79.29836408919209</v>
+        <v>79.64054426790221</v>
       </c>
       <c r="T14">
-        <v>113.4173302771076</v>
+        <v>111.9288060707105</v>
       </c>
       <c r="U14">
-        <v>202.6881136468232</v>
+        <v>208.9067242959009</v>
       </c>
       <c r="V14">
         <v>391.0904795120989</v>
       </c>
       <c r="W14">
-        <v>328.808070616857</v>
+        <v>328.1510511136108</v>
       </c>
       <c r="Z14">
-        <v>1.262599526867625E-13</v>
+        <v>1.190543601434479E-13</v>
       </c>
       <c r="AA14">
-        <v>34.08089729263259</v>
+        <v>33.42666687937166</v>
       </c>
       <c r="AB14">
         <v>27.67552092071268</v>
@@ -2253,16 +2253,16 @@
         <v>0.2694859428032323</v>
       </c>
       <c r="AH14">
-        <v>1936.623859782474</v>
+        <v>1959.044199174394</v>
       </c>
       <c r="AJ14">
-        <v>60.23782392091884</v>
+        <v>61.19819055240928</v>
       </c>
       <c r="AK14">
-        <v>521.765263905949</v>
+        <v>532.4654323557518</v>
       </c>
       <c r="AL14">
-        <v>106.5576396496167</v>
+        <v>106.8587920107782</v>
       </c>
       <c r="AM14">
         <v>52.49921122250679</v>
@@ -2271,25 +2271,25 @@
         <v>24.05868922444462</v>
       </c>
       <c r="AO14">
-        <v>374.5291086451645</v>
+        <v>368.3538232658051</v>
       </c>
       <c r="AP14">
         <v>2873.440187058914</v>
       </c>
       <c r="AQ14">
-        <v>204.5406245584257</v>
+        <v>204.2558616193948</v>
       </c>
       <c r="AR14">
-        <v>201.3825451129178</v>
+        <v>207.0920961062994</v>
       </c>
       <c r="AS14">
-        <v>10.42676118218669</v>
+        <v>10.43109786579504</v>
       </c>
       <c r="AT14">
-        <v>45.66567917605976</v>
+        <v>48.58217384197194</v>
       </c>
       <c r="AU14">
-        <v>348.7305918461557</v>
+        <v>353.2820006435614</v>
       </c>
       <c r="AV14">
         <v>1</v>
@@ -2302,76 +2302,76 @@
         </is>
       </c>
       <c r="B15">
-        <v>357.7644610175856</v>
+        <v>365.049264441367</v>
       </c>
       <c r="C15">
-        <v>64.30693912341638</v>
+        <v>65.505932730225</v>
       </c>
       <c r="D15">
-        <v>5594.847214903799</v>
+        <v>5604.611537542254</v>
       </c>
       <c r="E15">
-        <v>91.20587493110777</v>
+        <v>90.63738072607663</v>
       </c>
       <c r="F15">
-        <v>318.5760725663177</v>
+        <v>326.2253602976372</v>
       </c>
       <c r="G15">
-        <v>20.64240360568746</v>
+        <v>20.58072205602393</v>
       </c>
       <c r="H15">
         <v>21.47982135996927</v>
       </c>
       <c r="I15">
-        <v>182.6611231723595</v>
+        <v>188.5818413368514</v>
       </c>
       <c r="J15">
-        <v>50.49470635537054</v>
+        <v>50.89448105948505</v>
       </c>
       <c r="K15">
-        <v>-5.915799143886172E-15</v>
+        <v>-7.905641999438719E-15</v>
       </c>
       <c r="L15">
-        <v>3665.14855503969</v>
+        <v>3675.387423385743</v>
       </c>
       <c r="M15">
-        <v>826.9730848214308</v>
+        <v>802.163744530035</v>
       </c>
       <c r="N15">
-        <v>1000.978551705484</v>
+        <v>1003.499516651374</v>
       </c>
       <c r="O15">
-        <v>72.0438035688133</v>
+        <v>71.27599320385505</v>
       </c>
       <c r="P15">
-        <v>2.196935458167331</v>
+        <v>2.385195043952132</v>
       </c>
       <c r="S15">
-        <v>3.312861259538954</v>
+        <v>3.157449668052601</v>
       </c>
       <c r="T15">
         <v>6.677878086091871</v>
       </c>
       <c r="U15">
-        <v>8.302001048492793</v>
+        <v>8.502374431311583</v>
       </c>
       <c r="V15">
-        <v>105.1417882013693</v>
+        <v>104.7895525727069</v>
       </c>
       <c r="W15">
-        <v>189.9491216044831</v>
+        <v>189.9893961342991</v>
       </c>
       <c r="Z15">
-        <v>1.556979026707701E-14</v>
+        <v>1.509045587230991E-14</v>
       </c>
       <c r="AA15">
-        <v>11.1055152471747</v>
+        <v>10.68821964086377</v>
       </c>
       <c r="AB15">
-        <v>5.194462144308943</v>
+        <v>5.121255939866947</v>
       </c>
       <c r="AC15">
-        <v>2.063984345337407E-16</v>
+        <v>1.658916435897729E-16</v>
       </c>
       <c r="AD15">
         <v>1.03155306216269</v>
@@ -2386,43 +2386,43 @@
         <v>0.6947002930978334</v>
       </c>
       <c r="AH15">
-        <v>1348.027185219588</v>
+        <v>1335.205546996492</v>
       </c>
       <c r="AJ15">
-        <v>29.8412622664133</v>
+        <v>29.32846658359021</v>
       </c>
       <c r="AK15">
-        <v>655.9368057105571</v>
+        <v>646.5676917529272</v>
       </c>
       <c r="AL15">
-        <v>173.8675610250219</v>
+        <v>174.0422055936752</v>
       </c>
       <c r="AM15">
-        <v>1084.721449923174</v>
+        <v>1091.144081238708</v>
       </c>
       <c r="AN15">
-        <v>25.77257946896036</v>
+        <v>25.51992696844622</v>
       </c>
       <c r="AO15">
-        <v>69.57830254773263</v>
+        <v>67.83173156188727</v>
       </c>
       <c r="AP15">
-        <v>625.7126515469354</v>
+        <v>619.2841822262548</v>
       </c>
       <c r="AQ15">
-        <v>37.34626431124438</v>
+        <v>37.83599604810266</v>
       </c>
       <c r="AR15">
-        <v>20.75738817746239</v>
+        <v>21.70605015460918</v>
       </c>
       <c r="AS15">
-        <v>3.864291192817406</v>
+        <v>3.852976343627308</v>
       </c>
       <c r="AT15">
         <v>5.264389053214085</v>
       </c>
       <c r="AU15">
-        <v>93.99051634296788</v>
+        <v>92.83800262123192</v>
       </c>
       <c r="AV15">
         <v>1</v>
@@ -2435,46 +2435,46 @@
         </is>
       </c>
       <c r="B16">
-        <v>291.4390704453126</v>
+        <v>293.0162917761922</v>
       </c>
       <c r="C16">
-        <v>80.10491253916459</v>
+        <v>78.5603125884017</v>
       </c>
       <c r="D16">
-        <v>6996.820680797216</v>
+        <v>7011.047009966777</v>
       </c>
       <c r="E16">
-        <v>171.184136872569</v>
+        <v>171.7768213058419</v>
       </c>
       <c r="F16">
-        <v>282.2641288229636</v>
+        <v>283.3909717114569</v>
       </c>
       <c r="G16">
-        <v>4.245579507162223</v>
+        <v>4.251135005973715</v>
       </c>
       <c r="H16">
         <v>53.79397032866993</v>
       </c>
       <c r="I16">
-        <v>180.7882249916112</v>
+        <v>181.5534443910403</v>
       </c>
       <c r="J16">
-        <v>42.39975384988481</v>
+        <v>42.15599915801532</v>
       </c>
       <c r="K16">
         <v>1.627144785433848E-14</v>
       </c>
       <c r="L16">
-        <v>4938.097759055293</v>
+        <v>4944.498821336392</v>
       </c>
       <c r="M16">
-        <v>606.8969612801482</v>
+        <v>610.672728056137</v>
       </c>
       <c r="N16">
-        <v>1245.567120769511</v>
+        <v>1251.135344978167</v>
       </c>
       <c r="O16">
-        <v>146.0338744724025</v>
+        <v>147.8030434782609</v>
       </c>
       <c r="P16">
         <v>3.051979000954502</v>
@@ -2483,28 +2483,28 @@
         <v>33.71763317599461</v>
       </c>
       <c r="S16">
-        <v>17.87985999411199</v>
+        <v>17.55570483670892</v>
       </c>
       <c r="T16">
-        <v>8.024679851184649</v>
+        <v>7.958107090916451</v>
       </c>
       <c r="U16">
         <v>5.799686100866053</v>
       </c>
       <c r="V16">
-        <v>76.63342910560525</v>
+        <v>76.26146191646193</v>
       </c>
       <c r="W16">
-        <v>179.1273568510987</v>
+        <v>179.8604874401914</v>
       </c>
       <c r="Z16">
-        <v>-2.03558877123509E-14</v>
+        <v>-2.079981912244289E-14</v>
       </c>
       <c r="AA16">
-        <v>2.879939694927279</v>
+        <v>2.788031994047619</v>
       </c>
       <c r="AB16">
-        <v>1.995154721626862</v>
+        <v>1.93417953535261</v>
       </c>
       <c r="AC16">
         <v>9.530354110780047E-17</v>
@@ -2516,43 +2516,43 @@
         <v>2.437539222821127</v>
       </c>
       <c r="AH16">
-        <v>2875.304034390516</v>
+        <v>2905.959279636983</v>
       </c>
       <c r="AJ16">
-        <v>56.73081840255633</v>
+        <v>57.31567220052083</v>
       </c>
       <c r="AK16">
-        <v>950.3996894883813</v>
+        <v>950.0647544642858</v>
       </c>
       <c r="AL16">
-        <v>145.9637409928347</v>
+        <v>146.1036823966066</v>
       </c>
       <c r="AM16">
-        <v>530.4818836437121</v>
+        <v>532.3398642714571</v>
       </c>
       <c r="AN16">
-        <v>56.70973700887199</v>
+        <v>56.65212465231518</v>
       </c>
       <c r="AO16">
-        <v>19.65829846993825</v>
+        <v>19.77858241203185</v>
       </c>
       <c r="AP16">
-        <v>482.3446206170599</v>
+        <v>482.3617395609836</v>
       </c>
       <c r="AQ16">
-        <v>29.57987938026213</v>
+        <v>29.77092303268475</v>
       </c>
       <c r="AR16">
-        <v>7.682049072411729</v>
+        <v>7.586612700747601</v>
       </c>
       <c r="AS16">
-        <v>6.263969477183439</v>
+        <v>6.304156136556369</v>
       </c>
       <c r="AT16">
         <v>0.5393222515324018</v>
       </c>
       <c r="AU16">
-        <v>42.31083223451127</v>
+        <v>42.36204836415362</v>
       </c>
       <c r="AV16">
         <v>1</v>
@@ -2695,73 +2695,73 @@
         </is>
       </c>
       <c r="B18">
-        <v>321.558614616558</v>
+        <v>321.3788232848546</v>
       </c>
       <c r="C18">
-        <v>76.79050534878537</v>
+        <v>75.37835776302418</v>
       </c>
       <c r="D18">
-        <v>7344.553798245614</v>
+        <v>7358.862816338235</v>
       </c>
       <c r="E18">
-        <v>162.7166963482641</v>
+        <v>162.1724347989076</v>
       </c>
       <c r="F18">
-        <v>308.0231876758999</v>
+        <v>307.6842273727403</v>
       </c>
       <c r="G18">
-        <v>3.076966858789625</v>
+        <v>3.102628166236918</v>
       </c>
       <c r="H18">
         <v>1.465901960784314</v>
       </c>
       <c r="I18">
-        <v>192.1125416289201</v>
+        <v>193.2695890892063</v>
       </c>
       <c r="J18">
-        <v>62.13437882607131</v>
+        <v>61.96596182682876</v>
       </c>
       <c r="K18">
         <v>1.002715950275063E-14</v>
       </c>
       <c r="L18">
-        <v>5410.822688450339</v>
+        <v>5437.52676506927</v>
       </c>
       <c r="M18">
-        <v>612.6089078947368</v>
+        <v>615.1441567053653</v>
       </c>
       <c r="N18">
-        <v>1192.041047060297</v>
+        <v>1190.163223511674</v>
       </c>
       <c r="O18">
-        <v>132.4650766580534</v>
+        <v>132.2281050047097</v>
       </c>
       <c r="P18">
-        <v>5.05320796460177</v>
+        <v>5.066235169618905</v>
       </c>
       <c r="S18">
-        <v>8.179900921429818</v>
+        <v>7.713892134656915</v>
       </c>
       <c r="T18">
-        <v>2.886544113257357</v>
+        <v>2.857364211072413</v>
       </c>
       <c r="U18">
         <v>2.444430619421152</v>
       </c>
       <c r="V18">
-        <v>110.699778597786</v>
+        <v>110.7468147647315</v>
       </c>
       <c r="W18">
-        <v>182.9373819823209</v>
+        <v>179.6112328991471</v>
       </c>
       <c r="Z18">
-        <v>-1.130913888405465E-14</v>
+        <v>-1.076275337003049E-14</v>
       </c>
       <c r="AA18">
-        <v>1.192546403712297</v>
+        <v>1.176563339903243</v>
       </c>
       <c r="AB18">
-        <v>1.582942839963171</v>
+        <v>1.64272304713637</v>
       </c>
       <c r="AC18">
         <v>3.395429935321545E-17</v>
@@ -2776,43 +2776,43 @@
         <v>0.2359013659281808</v>
       </c>
       <c r="AH18">
-        <v>2753.727165225901</v>
+        <v>2803.547804307708</v>
       </c>
       <c r="AJ18">
-        <v>48.79836248694467</v>
+        <v>49.55596049046321</v>
       </c>
       <c r="AK18">
-        <v>1034.992305270732</v>
+        <v>1035.027374036281</v>
       </c>
       <c r="AL18">
-        <v>167.6571106442577</v>
+        <v>167.9765291367977</v>
       </c>
       <c r="AM18">
-        <v>1030.696044189505</v>
+        <v>1029.777160996023</v>
       </c>
       <c r="AN18">
-        <v>88.5120352708787</v>
+        <v>88.64355233447448</v>
       </c>
       <c r="AO18">
-        <v>28.34323659306002</v>
+        <v>28.34175074081208</v>
       </c>
       <c r="AP18">
-        <v>523.5928768750928</v>
+        <v>527.5751469798095</v>
       </c>
       <c r="AQ18">
-        <v>25.77509433962264</v>
+        <v>25.58035498411385</v>
       </c>
       <c r="AR18">
-        <v>11.28688509874327</v>
+        <v>11.69940766256815</v>
       </c>
       <c r="AS18">
-        <v>5.29785731104309</v>
+        <v>5.288932419196866</v>
       </c>
       <c r="AT18">
         <v>0.1449608633696535</v>
       </c>
       <c r="AU18">
-        <v>28.35798620094873</v>
+        <v>28.55201289144608</v>
       </c>
       <c r="AV18">
         <v>1</v>
@@ -2825,85 +2825,88 @@
         </is>
       </c>
       <c r="B19">
-        <v>831.1411416349174</v>
+        <v>829.4855329080674</v>
       </c>
       <c r="C19">
-        <v>152.9423312368973</v>
+        <v>152.2037440182142</v>
       </c>
       <c r="D19">
-        <v>6739.003798312177</v>
+        <v>6794.649701330532</v>
       </c>
       <c r="E19">
-        <v>579.8809178338358</v>
+        <v>580.0706872561648</v>
       </c>
       <c r="F19">
-        <v>748.2371907687199</v>
+        <v>747.9642106595022</v>
       </c>
       <c r="G19">
-        <v>78.4037210372871</v>
+        <v>77.87194500940805</v>
       </c>
       <c r="H19">
-        <v>1.114156500116559</v>
+        <v>1.083875587820746</v>
       </c>
       <c r="I19">
         <v>290.7155719199224</v>
       </c>
       <c r="J19">
-        <v>92.58359732217734</v>
+        <v>92.49063409424643</v>
       </c>
       <c r="K19">
-        <v>9.01885046691469E-15</v>
+        <v>1.125286206995833E-14</v>
       </c>
       <c r="L19">
-        <v>3530.148246852933</v>
+        <v>3545.531069450581</v>
       </c>
       <c r="M19">
-        <v>2047.749087503746</v>
+        <v>2042.615196069754</v>
       </c>
       <c r="N19">
-        <v>880.6605726330586</v>
+        <v>882.2154826089318</v>
       </c>
       <c r="O19">
-        <v>380.7239411893422</v>
+        <v>381.5012748171368</v>
       </c>
       <c r="P19">
         <v>14.8962916975102</v>
       </c>
       <c r="Q19">
-        <v>0.7121344119477288</v>
+        <v>0.660372508109745</v>
       </c>
       <c r="R19">
         <v>0.4830715219652364</v>
       </c>
       <c r="S19">
-        <v>57.43528956865308</v>
+        <v>57.10959851932287</v>
       </c>
       <c r="T19">
-        <v>122.0721735045412</v>
+        <v>120.3850833685108</v>
       </c>
       <c r="U19">
-        <v>104.0514904924074</v>
+        <v>104.2967388488626</v>
       </c>
       <c r="V19">
-        <v>199.6363684020246</v>
+        <v>199.2262237975066</v>
       </c>
       <c r="W19">
-        <v>267.6942153144239</v>
+        <v>268.7204671012183</v>
       </c>
       <c r="Z19">
-        <v>3.771452881734343E-14</v>
+        <v>3.735350238562355E-14</v>
       </c>
       <c r="AA19">
-        <v>20.97509145475578</v>
+        <v>21.04575470466943</v>
       </c>
       <c r="AB19">
-        <v>55.96742761701785</v>
+        <v>54.61515075885329</v>
       </c>
       <c r="AC19">
-        <v>-6.519675281526367E-16</v>
+        <v>3.166764281939165E-16</v>
       </c>
       <c r="AD19">
-        <v>1.058232020667504</v>
+        <v>1.009484602917342</v>
+      </c>
+      <c r="AE19">
+        <v>9.70717674858223</v>
       </c>
       <c r="AF19">
         <v>0.6118350421243341</v>
@@ -2912,43 +2915,43 @@
         <v>0.3103345454545466</v>
       </c>
       <c r="AH19">
-        <v>2632.805727536407</v>
+        <v>2640.941835654596</v>
       </c>
       <c r="AJ19">
-        <v>55.45168360744879</v>
+        <v>56.552177877429</v>
       </c>
       <c r="AK19">
-        <v>405.4835174941225</v>
+        <v>405.3171321747342</v>
       </c>
       <c r="AL19">
-        <v>86.90551884667367</v>
+        <v>86.98162599250173</v>
       </c>
       <c r="AM19">
-        <v>41.32278752436648</v>
+        <v>40.73331525316469</v>
       </c>
       <c r="AN19">
-        <v>25.24876890551309</v>
+        <v>25.36632053577349</v>
       </c>
       <c r="AO19">
-        <v>131.9517217753949</v>
+        <v>132.9133371764807</v>
       </c>
       <c r="AP19">
-        <v>1558.851002938667</v>
+        <v>1556.629935772761</v>
       </c>
       <c r="AQ19">
-        <v>220.1558575279708</v>
+        <v>219.2288405077654</v>
       </c>
       <c r="AR19">
-        <v>62.70764761961508</v>
+        <v>63.22454322501533</v>
       </c>
       <c r="AS19">
-        <v>44.008586333302</v>
+        <v>43.95002735121281</v>
       </c>
       <c r="AT19">
-        <v>1.421895635673624</v>
+        <v>1.419025869197149</v>
       </c>
       <c r="AU19">
-        <v>120.0037066814528</v>
+        <v>121.2159586344712</v>
       </c>
       <c r="AV19">
         <v>1</v>
@@ -2973,7 +2976,7 @@
         <v>378.530268288201</v>
       </c>
       <c r="F20">
-        <v>795.1421101700079</v>
+        <v>795.8704575476386</v>
       </c>
       <c r="G20">
         <v>74.30895041198855</v>
@@ -2982,7 +2985,7 @@
         <v>9.326571642910727</v>
       </c>
       <c r="I20">
-        <v>252.8451762110522</v>
+        <v>253.2489088300924</v>
       </c>
       <c r="J20">
         <v>81.26611483277996</v>
@@ -3000,7 +3003,7 @@
         <v>902.7588777680462</v>
       </c>
       <c r="O20">
-        <v>252.4300090094362</v>
+        <v>257.6800438269303</v>
       </c>
       <c r="P20">
         <v>9.093369310152365</v>
@@ -3012,7 +3015,7 @@
         <v>0.4500406805860108</v>
       </c>
       <c r="S20">
-        <v>84.73842292239345</v>
+        <v>85.38551526202301</v>
       </c>
       <c r="T20">
         <v>176.7574058280028</v>
@@ -3021,16 +3024,16 @@
         <v>34.26633079900855</v>
       </c>
       <c r="V20">
-        <v>300.8105811423964</v>
+        <v>302.0169595008635</v>
       </c>
       <c r="W20">
-        <v>284.1735439362736</v>
+        <v>284.4338002296211</v>
       </c>
       <c r="Z20">
-        <v>2.497931604560911E-14</v>
+        <v>1.769752345151047E-14</v>
       </c>
       <c r="AA20">
-        <v>24.45198143187045</v>
+        <v>24.56054658245745</v>
       </c>
       <c r="AB20">
         <v>46.46207692312383</v>
@@ -3051,7 +3054,7 @@
         <v>1398.226863494702</v>
       </c>
       <c r="AK20">
-        <v>725.489685459114</v>
+        <v>719.5215464961666</v>
       </c>
       <c r="AL20">
         <v>93.31445792487625</v>
@@ -3075,7 +3078,7 @@
         <v>69.17810064424573</v>
       </c>
       <c r="AS20">
-        <v>12.6261611504851</v>
+        <v>12.65825112034934</v>
       </c>
       <c r="AT20">
         <v>168.5801743586084</v>
@@ -3224,22 +3227,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>638.6891898093417</v>
+        <v>651.6748020152024</v>
       </c>
       <c r="C22">
-        <v>150.9686019679605</v>
+        <v>186.6791251495875</v>
       </c>
       <c r="D22">
-        <v>6486.945039533327</v>
+        <v>6384.226143463397</v>
       </c>
       <c r="E22">
-        <v>619.9970199744042</v>
+        <v>615.8500992708424</v>
       </c>
       <c r="F22">
-        <v>556.9778057321757</v>
+        <v>557.852160900317</v>
       </c>
       <c r="G22">
-        <v>79.21314675951569</v>
+        <v>79.71305851231341</v>
       </c>
       <c r="H22">
         <v>7.393030927835052</v>
@@ -3248,52 +3251,52 @@
         <v>203.677351311801</v>
       </c>
       <c r="J22">
-        <v>47.57662715714164</v>
+        <v>48.10658846944435</v>
       </c>
       <c r="K22">
         <v>2.452554866325957E-15</v>
       </c>
       <c r="L22">
-        <v>2884.141888816832</v>
+        <v>2872.65762339319</v>
       </c>
       <c r="M22">
-        <v>2374.060967217833</v>
+        <v>2364.98568848574</v>
       </c>
       <c r="N22">
-        <v>1117.82554002121</v>
+        <v>1109.801537462103</v>
       </c>
       <c r="O22">
-        <v>554.7411823598095</v>
+        <v>544.8477813862855</v>
       </c>
       <c r="P22">
-        <v>13.40371279393796</v>
+        <v>14.31936575117228</v>
       </c>
       <c r="Q22">
         <v>0.008253024506255816</v>
       </c>
       <c r="S22">
-        <v>46.07677786843765</v>
+        <v>47.75434828776249</v>
       </c>
       <c r="T22">
-        <v>71.48853168715587</v>
+        <v>73.54359520400858</v>
       </c>
       <c r="U22">
-        <v>57.40595109536271</v>
+        <v>57.11619577820486</v>
       </c>
       <c r="V22">
-        <v>160.1128887958049</v>
+        <v>157.6922477686834</v>
       </c>
       <c r="W22">
-        <v>234.0157372262774</v>
+        <v>234.2572652068127</v>
       </c>
       <c r="Z22">
-        <v>-2.659003360762531E-14</v>
+        <v>-2.745746471463198E-14</v>
       </c>
       <c r="AA22">
-        <v>17.36832762194483</v>
+        <v>17.68066239193908</v>
       </c>
       <c r="AB22">
-        <v>64.104336935167</v>
+        <v>64.32895469923935</v>
       </c>
       <c r="AC22">
         <v>-2.121270441452894E-15</v>
@@ -3308,43 +3311,43 @@
         <v>0.003866172025281671</v>
       </c>
       <c r="AH22">
-        <v>1816.00229332501</v>
+        <v>1804.3208117506</v>
       </c>
       <c r="AJ22">
-        <v>40.51471405928525</v>
+        <v>39.93414588012767</v>
       </c>
       <c r="AK22">
-        <v>721.25747719356</v>
+        <v>718.0784921000154</v>
       </c>
       <c r="AL22">
-        <v>92.83584864012353</v>
+        <v>91.37257955936353</v>
       </c>
       <c r="AM22">
-        <v>26.82640379784006</v>
+        <v>27.36416415427884</v>
       </c>
       <c r="AN22">
-        <v>23.85031912715728</v>
+        <v>23.60338726812127</v>
       </c>
       <c r="AO22">
-        <v>76.31042567803429</v>
+        <v>78.48432361516056</v>
       </c>
       <c r="AP22">
-        <v>1742.589515567835</v>
+        <v>1742.057793187348</v>
       </c>
       <c r="AQ22">
-        <v>150.5866521995416</v>
+        <v>150.9050626822157</v>
       </c>
       <c r="AR22">
-        <v>54.11215648027741</v>
+        <v>59.58777434828825</v>
       </c>
       <c r="AS22">
-        <v>12.87079444658696</v>
+        <v>12.38587170166198</v>
       </c>
       <c r="AT22">
         <v>7.371706646819717</v>
       </c>
       <c r="AU22">
-        <v>335.1322091530582</v>
+        <v>332.2377596531077</v>
       </c>
       <c r="AV22">
         <v>1</v>
@@ -3357,22 +3360,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>405.9330603392818</v>
+        <v>425.6495634788404</v>
       </c>
       <c r="C23">
         <v>33.43016992961698</v>
       </c>
       <c r="D23">
-        <v>5328.321989900858</v>
+        <v>4975.777597384134</v>
       </c>
       <c r="E23">
-        <v>161.2899871266379</v>
+        <v>154.7064210010415</v>
       </c>
       <c r="F23">
-        <v>378.9341546061154</v>
+        <v>408.1368560479841</v>
       </c>
       <c r="G23">
-        <v>8.314697869237811</v>
+        <v>8.342652301834544</v>
       </c>
       <c r="H23">
         <v>37.97439035998615</v>
@@ -3387,22 +3390,22 @@
         <v>-1.534692806646624E-14</v>
       </c>
       <c r="L23">
-        <v>2455.749916885717</v>
+        <v>2434.23419898303</v>
       </c>
       <c r="M23">
-        <v>1171.809780823175</v>
+        <v>1206.987039147216</v>
       </c>
       <c r="N23">
-        <v>1654.247831668484</v>
+        <v>1647.12532640208</v>
       </c>
       <c r="O23">
-        <v>145.4503925535566</v>
+        <v>141.7184264720584</v>
       </c>
       <c r="P23">
         <v>4.84756237679643</v>
       </c>
       <c r="S23">
-        <v>11.70025905942798</v>
+        <v>12.26915735388534</v>
       </c>
       <c r="T23">
         <v>14.93405394990366</v>
@@ -3411,16 +3414,16 @@
         <v>19.02889005259758</v>
       </c>
       <c r="V23">
-        <v>240.4124573779354</v>
+        <v>255.9038083416087</v>
       </c>
       <c r="W23">
-        <v>114.790159407184</v>
+        <v>115.8315017533883</v>
       </c>
       <c r="Z23">
         <v>2.558578501690875E-15</v>
       </c>
       <c r="AA23">
-        <v>5.455019706168157</v>
+        <v>5.721727324424225</v>
       </c>
       <c r="AB23">
         <v>3.872188906195916</v>
@@ -3432,31 +3435,31 @@
         <v>37.97439035998615</v>
       </c>
       <c r="AH23">
-        <v>747.2993643579418</v>
+        <v>753.6834393187527</v>
       </c>
       <c r="AJ23">
-        <v>13.19621665544673</v>
+        <v>13.23689334068492</v>
       </c>
       <c r="AK23">
-        <v>901.4335826701729</v>
+        <v>908.9925841386205</v>
       </c>
       <c r="AL23">
-        <v>125.6519104027669</v>
+        <v>122.7056495134918</v>
       </c>
       <c r="AM23">
         <v>53.30954009433962</v>
       </c>
       <c r="AN23">
-        <v>33.52521031496038</v>
+        <v>37.53077130429455</v>
       </c>
       <c r="AO23">
-        <v>198.2237839552116</v>
+        <v>163.7916441875401</v>
       </c>
       <c r="AP23">
-        <v>805.4523550712095</v>
+        <v>814.9076806107249</v>
       </c>
       <c r="AQ23">
-        <v>15.04027135070786</v>
+        <v>15.15720747252747</v>
       </c>
       <c r="AR23">
         <v>13.19459932804416</v>
@@ -3465,7 +3468,7 @@
         <v>3.814679993240846</v>
       </c>
       <c r="AU23">
-        <v>213.4158076003532</v>
+        <v>243.467528550149</v>
       </c>
       <c r="AV23">
         <v>1</v>
@@ -3544,7 +3547,7 @@
         <v>267.2991257946267</v>
       </c>
       <c r="Z24">
-        <v>3.265964983221625E-14</v>
+        <v>3.25991732253716E-14</v>
       </c>
       <c r="AA24">
         <v>21.89121191629795</v>
@@ -3580,7 +3583,7 @@
         <v>87.39363905325443</v>
       </c>
       <c r="AM24">
-        <v>25.27516974169742</v>
+        <v>25.33384621974624</v>
       </c>
       <c r="AN24">
         <v>32.36308133430938</v>
@@ -3617,22 +3620,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>961.8720139066908</v>
+        <v>961.2834531502424</v>
       </c>
       <c r="C25">
-        <v>92.04650757575757</v>
+        <v>92.00885013525112</v>
       </c>
       <c r="D25">
-        <v>6742.376989425107</v>
+        <v>6740.79479215578</v>
       </c>
       <c r="E25">
-        <v>492.388457869577</v>
+        <v>491.484647553352</v>
       </c>
       <c r="F25">
-        <v>827.4780925154007</v>
+        <v>827.0467181008902</v>
       </c>
       <c r="G25">
-        <v>118.32339270904</v>
+        <v>118.3331940789474</v>
       </c>
       <c r="H25">
         <v>1.369760514840421</v>
@@ -3641,25 +3644,25 @@
         <v>230.4928383356719</v>
       </c>
       <c r="J25">
-        <v>82.37331214028336</v>
+        <v>82.4307103478867</v>
       </c>
       <c r="K25">
         <v>-1.235700942162778E-14</v>
       </c>
       <c r="L25">
-        <v>2917.626195382961</v>
+        <v>2915.583811443721</v>
       </c>
       <c r="M25">
-        <v>2755.595962926831</v>
+        <v>2744.517705634227</v>
       </c>
       <c r="N25">
-        <v>1084.586202808403</v>
+        <v>1084.456371298406</v>
       </c>
       <c r="O25">
-        <v>304.9162703024443</v>
+        <v>304.3778771658757</v>
       </c>
       <c r="P25">
-        <v>32.27975798869263</v>
+        <v>31.94989983048236</v>
       </c>
       <c r="Q25">
         <v>1.933270295595877</v>
@@ -3668,28 +3671,28 @@
         <v>10.95951879395962</v>
       </c>
       <c r="S25">
-        <v>50.13765196676725</v>
+        <v>50.09876536514867</v>
       </c>
       <c r="T25">
-        <v>133.1111790741765</v>
+        <v>132.3393709131905</v>
       </c>
       <c r="U25">
-        <v>93.92930347586636</v>
+        <v>93.85347368421053</v>
       </c>
       <c r="V25">
-        <v>294.5856996654202</v>
+        <v>293.859482023297</v>
       </c>
       <c r="W25">
-        <v>280.5774176468284</v>
+        <v>280.5228610763455</v>
       </c>
       <c r="Z25">
-        <v>3.07282262834242E-14</v>
+        <v>3.095328950463569E-14</v>
       </c>
       <c r="AA25">
-        <v>43.70482324975359</v>
+        <v>43.71964378801042</v>
       </c>
       <c r="AB25">
-        <v>73.2819932829555</v>
+        <v>73.43926779960694</v>
       </c>
       <c r="AC25">
         <v>-3.031606512162975E-15</v>
@@ -3707,43 +3710,43 @@
         <v>0.5513173933427098</v>
       </c>
       <c r="AH25">
-        <v>2074.150530314952</v>
+        <v>2071.737492795389</v>
       </c>
       <c r="AJ25">
-        <v>58.68854039693701</v>
+        <v>58.71738217763517</v>
       </c>
       <c r="AK25">
-        <v>439.837430523918</v>
+        <v>439.9264203855706</v>
       </c>
       <c r="AL25">
-        <v>98.23410853569644</v>
+        <v>98.24004366812228</v>
       </c>
       <c r="AM25">
-        <v>30.78268005879471</v>
+        <v>30.89711877757785</v>
       </c>
       <c r="AN25">
-        <v>18.77454162679426</v>
+        <v>18.70504788709334</v>
       </c>
       <c r="AO25">
-        <v>52.22162600539401</v>
+        <v>52.48758275382475</v>
       </c>
       <c r="AP25">
-        <v>2190.893646774453</v>
+        <v>2185.114691084215</v>
       </c>
       <c r="AQ25">
-        <v>240.3662410218267</v>
+        <v>240.5148792908336</v>
       </c>
       <c r="AR25">
         <v>43.51724447513812</v>
       </c>
       <c r="AS25">
-        <v>15.14837801096192</v>
+        <v>15.10559790819291</v>
       </c>
       <c r="AT25">
         <v>7.199172993492407</v>
       </c>
       <c r="AU25">
-        <v>154.1675230044175</v>
+        <v>154.4314161813904</v>
       </c>
       <c r="AV25">
         <v>1</v>
@@ -3874,88 +3877,88 @@
         </is>
       </c>
       <c r="B27">
-        <v>984.6613464315574</v>
+        <v>985.144291541897</v>
       </c>
       <c r="C27">
-        <v>96.85011402468436</v>
+        <v>97.33648772834249</v>
       </c>
       <c r="D27">
-        <v>6233.972346447952</v>
+        <v>6232.850597264043</v>
       </c>
       <c r="E27">
-        <v>336.657452133273</v>
+        <v>336.9498015250286</v>
       </c>
       <c r="F27">
-        <v>903.521941924335</v>
+        <v>903.6730527342636</v>
       </c>
       <c r="G27">
-        <v>66.40553221288515</v>
+        <v>66.42359538659821</v>
       </c>
       <c r="H27">
-        <v>0.7272419832720681</v>
+        <v>0.724898504922815</v>
       </c>
       <c r="I27">
-        <v>225.471025688377</v>
+        <v>225.6264645806688</v>
       </c>
       <c r="J27">
-        <v>61.91741285670048</v>
+        <v>62.03513850766026</v>
       </c>
       <c r="K27">
-        <v>7.644815836747533E-15</v>
+        <v>7.688239454955409E-15</v>
       </c>
       <c r="L27">
-        <v>2939.211647692496</v>
+        <v>2938.779573582998</v>
       </c>
       <c r="M27">
-        <v>2277.992139861865</v>
+        <v>2272.5925710672</v>
       </c>
       <c r="N27">
-        <v>881.0105422357938</v>
+        <v>882.1984578744764</v>
       </c>
       <c r="O27">
-        <v>141.8129115341545</v>
+        <v>142.0199807211495</v>
       </c>
       <c r="P27">
-        <v>53.5448124139083</v>
+        <v>53.7356090487239</v>
       </c>
       <c r="Q27">
-        <v>1.303768557289684</v>
+        <v>1.265490429438493</v>
       </c>
       <c r="R27">
         <v>0.391877288361256</v>
       </c>
       <c r="S27">
-        <v>61.34563792507818</v>
+        <v>61.41032654260432</v>
       </c>
       <c r="T27">
-        <v>226.837930250117</v>
+        <v>226.9160291360162</v>
       </c>
       <c r="U27">
-        <v>90.90912729221913</v>
+        <v>90.89088953163851</v>
       </c>
       <c r="V27">
-        <v>311.6924208862998</v>
+        <v>311.8241777747552</v>
       </c>
       <c r="W27">
-        <v>216.9638113400127</v>
+        <v>216.9661100524059</v>
       </c>
       <c r="Z27">
-        <v>3.985674411610244E-14</v>
+        <v>3.985802339362657E-14</v>
       </c>
       <c r="AA27">
-        <v>24.57464470602892</v>
+        <v>24.65260065111454</v>
       </c>
       <c r="AB27">
-        <v>42.94120987706486</v>
+        <v>42.86887031376708</v>
       </c>
       <c r="AC27">
-        <v>7.962875028518581E-16</v>
+        <v>7.797732714586282E-16</v>
       </c>
       <c r="AD27">
         <v>0.3071763771121409</v>
       </c>
       <c r="AE27">
-        <v>2.216957599118943</v>
+        <v>2.207743180090445</v>
       </c>
       <c r="AF27">
         <v>36.47156060606061</v>
@@ -3964,43 +3967,43 @@
         <v>0.1324166073286958</v>
       </c>
       <c r="AH27">
-        <v>2220.187604789995</v>
+        <v>2218.761419156039</v>
       </c>
       <c r="AJ27">
-        <v>54.12977607318107</v>
+        <v>54.23505548216644</v>
       </c>
       <c r="AK27">
-        <v>420.9186779911374</v>
+        <v>422.1737016286095</v>
       </c>
       <c r="AL27">
-        <v>94.53250177955429</v>
+        <v>94.55058266885379</v>
       </c>
       <c r="AM27">
-        <v>13.85927303244079</v>
+        <v>13.82911898700504</v>
       </c>
       <c r="AN27">
         <v>18.28115856201518</v>
       </c>
       <c r="AO27">
-        <v>54.13188763275099</v>
+        <v>54.11322350986235</v>
       </c>
       <c r="AP27">
-        <v>1632.630091790289</v>
+        <v>1630.560026160663</v>
       </c>
       <c r="AQ27">
-        <v>266.8468977311195</v>
+        <v>266.8474860579552</v>
       </c>
       <c r="AR27">
-        <v>132.4788648821375</v>
+        <v>132.6178726832292</v>
       </c>
       <c r="AS27">
-        <v>16.1118327588759</v>
+        <v>16.19726250826537</v>
       </c>
       <c r="AT27">
-        <v>3.049027973493434</v>
+        <v>3.025274558508285</v>
       </c>
       <c r="AU27">
-        <v>161.6110102802398</v>
+        <v>161.3584272812208</v>
       </c>
       <c r="AV27">
         <v>1</v>
@@ -4013,118 +4016,118 @@
         </is>
       </c>
       <c r="B28">
-        <v>501.3242046659597</v>
+        <v>508.2120899562148</v>
       </c>
       <c r="C28">
-        <v>46.31299189401768</v>
+        <v>48.93300974989403</v>
       </c>
       <c r="D28">
-        <v>8260.657360562143</v>
+        <v>8363.702772926119</v>
       </c>
       <c r="E28">
-        <v>159.4887790697674</v>
+        <v>159.8499564033482</v>
       </c>
       <c r="F28">
-        <v>466.1273370754448</v>
+        <v>466.6126730317984</v>
       </c>
       <c r="G28">
-        <v>10.71684719963952</v>
+        <v>10.8744979707076</v>
       </c>
       <c r="H28">
-        <v>10.99809000707175</v>
+        <v>13.67206952965235</v>
       </c>
       <c r="I28">
-        <v>157.9050703971119</v>
+        <v>159.0620146477527</v>
       </c>
       <c r="J28">
-        <v>29.30850253023861</v>
+        <v>29.56023592715232</v>
       </c>
       <c r="K28">
-        <v>-2.516802959798617E-15</v>
+        <v>-2.768892632169509E-15</v>
       </c>
       <c r="L28">
-        <v>5015.987195200342</v>
+        <v>5035.943636151573</v>
       </c>
       <c r="M28">
-        <v>1732.004210836278</v>
+        <v>1727.843276322929</v>
       </c>
       <c r="N28">
-        <v>1431.829684960481</v>
+        <v>1456.745573856517</v>
       </c>
       <c r="O28">
-        <v>119.246338028169</v>
+        <v>118.0721365712342</v>
       </c>
       <c r="P28">
-        <v>25.56626248708233</v>
+        <v>26.32735507025597</v>
       </c>
       <c r="Q28">
         <v>0.9081785102739727</v>
       </c>
       <c r="S28">
-        <v>1.056811757628068</v>
+        <v>1.081255989045626</v>
       </c>
       <c r="T28">
-        <v>13.60980841330315</v>
+        <v>13.54209793491865</v>
       </c>
       <c r="U28">
-        <v>99.55552768684092</v>
+        <v>102.245176730486</v>
       </c>
       <c r="V28">
-        <v>182.2088268389248</v>
+        <v>182.7395931026956</v>
       </c>
       <c r="W28">
-        <v>130.0576689189189</v>
+        <v>129.7322662675447</v>
       </c>
       <c r="Z28">
-        <v>1.271603733773182E-14</v>
+        <v>1.391861810460722E-14</v>
       </c>
       <c r="AA28">
-        <v>4.316036513545347</v>
+        <v>4.338099667898861</v>
       </c>
       <c r="AB28">
-        <v>4.647012211668929</v>
+        <v>4.581612842847452</v>
       </c>
       <c r="AC28">
-        <v>7.707582218414647E-17</v>
+        <v>7.821591862512283E-17</v>
       </c>
       <c r="AD28">
         <v>0.0008327328758771298</v>
       </c>
       <c r="AF28">
-        <v>17.3006440061268</v>
+        <v>20.92921848260125</v>
       </c>
       <c r="AG28">
         <v>1.699354707792208</v>
       </c>
       <c r="AH28">
-        <v>3243.038623721881</v>
+        <v>3238.079849067873</v>
       </c>
       <c r="AJ28">
-        <v>74.95777747625507</v>
+        <v>76.75247382675195</v>
       </c>
       <c r="AK28">
-        <v>1025.54998268262</v>
+        <v>1044.685190690236</v>
       </c>
       <c r="AL28">
-        <v>118.6586219031531</v>
+        <v>118.6014356938446</v>
       </c>
       <c r="AM28">
-        <v>60.42723063954682</v>
+        <v>57.43492291880781</v>
       </c>
       <c r="AN28">
-        <v>48.12835278154682</v>
+        <v>48.42029738330744</v>
       </c>
       <c r="AO28">
-        <v>138.5282464581668</v>
+        <v>143.5156356864252</v>
       </c>
       <c r="AP28">
-        <v>1179.840509013786</v>
+        <v>1163.641040713106</v>
       </c>
       <c r="AQ28">
-        <v>80.44934871794872</v>
+        <v>79.65346760710509</v>
       </c>
       <c r="AR28">
-        <v>15.52628247834777</v>
+        <v>15.22918199289869</v>
       </c>
       <c r="AS28">
         <v>6.807825722664433</v>
@@ -4133,7 +4136,7 @@
         <v>3.031521572910978</v>
       </c>
       <c r="AU28">
-        <v>350.8799200685126</v>
+        <v>349.861917922377</v>
       </c>
       <c r="AV28">
         <v>1</v>
